--- a/data/Spravochniki/oksm.xlsx
+++ b/data/Spravochniki/oksm.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId4"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId5"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId6"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="ИсторическиеКраткие" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="966">
-  <si>
-    <t>ОКСМ — Общероссийский классификатор стран мира</t>
-  </si>
-  <si>
-    <t>С изменением № 27/2021. Введено 01.06.2021 с правом досрочного применения в правоотношениях, возникших с 20.01.2021. Приказ Росстандарта от 12.04.2021 № 203-ст.</t>
-  </si>
-  <si>
-    <t>Всего записей — 251.</t>
-  </si>
-  <si>
-    <t>Подготовлено сайтом classifikators.ru</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
+  <si>
+    <t>ОКСМ — Общероссийский классификатор стран мира (единый справочник)</t>
+  </si>
+  <si>
+    <t>Актуальные краткие наименования (изм. 33/2024). Лист «ИсторическиеКраткие»: ДействуетС/ДействуетПо — для выпадающего списка по дате операции; все имена принимаются в проверках.</t>
+  </si>
+  <si>
+    <t>Всего записей — 253.</t>
+  </si>
+  <si>
+    <t>Собран из oksm2024.xlsx + diff shortname с oksm.xlsx (27/2021)</t>
   </si>
   <si>
     <t>ОКСМ онлайн</t>
@@ -946,10 +942,10 @@
     <t>FIN</t>
   </si>
   <si>
-    <t>ЭЛАНДСКИЕ ОСТРОВА</t>
-  </si>
-  <si>
-    <t>АХ</t>
+    <t>АЛАНДСКИЕ ОСТРОВА</t>
+  </si>
+  <si>
+    <t>AX</t>
   </si>
   <si>
     <t>ALA</t>
@@ -1030,7 +1026,7 @@
     <t>ГАМБИЯ</t>
   </si>
   <si>
-    <t>Республика Гамбия</t>
+    <t>Исламская Республика Гамбия</t>
   </si>
   <si>
     <t>GM</t>
@@ -1171,7 +1167,7 @@
     <t>ГАЙАНА</t>
   </si>
   <si>
-    <t>Республика Гайана</t>
+    <t>Кооперативная Республика Гайана</t>
   </si>
   <si>
     <t>GY</t>
@@ -1249,9 +1245,6 @@
     <t>ИСЛАНДИЯ</t>
   </si>
   <si>
-    <t>Республика Исландия</t>
-  </si>
-  <si>
     <t>IS</t>
   </si>
   <si>
@@ -1804,7 +1797,7 @@
     <t>NPL</t>
   </si>
   <si>
-    <t>НИДЕРЛАНДЫ</t>
+    <t>НИДЕРЛАНДЫ, КОРОЛЕВСТВО</t>
   </si>
   <si>
     <t>Королевство Нидерландов</t>
@@ -1921,7 +1914,7 @@
     <t>НИУЭ</t>
   </si>
   <si>
-    <t>Республика Ниуэ</t>
+    <t>Ниуэ</t>
   </si>
   <si>
     <t>NU</t>
@@ -2035,7 +2028,7 @@
     <t>ПАПУА-НОВАЯ ГВИНЕЯ</t>
   </si>
   <si>
-    <t>Независимое Государство  Папуа Новая Гвинея</t>
+    <t xml:space="preserve">Независимое Государство  Папуа Новая Гвинея</t>
   </si>
   <si>
     <t>PG</t>
@@ -2453,6 +2446,30 @@
     <t>ESP</t>
   </si>
   <si>
+    <t>ЮЖНЫЙ СУДАН</t>
+  </si>
+  <si>
+    <t>Республика Южный Судан</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>СУДАН</t>
+  </si>
+  <si>
+    <t>Республика Судан</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>SDN</t>
+  </si>
+  <si>
     <t>ЗАПАДНАЯ САХАРА</t>
   </si>
   <si>
@@ -2462,18 +2479,6 @@
     <t>ESH</t>
   </si>
   <si>
-    <t>СУДАН</t>
-  </si>
-  <si>
-    <t>Республика Судан</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>SDN</t>
-  </si>
-  <si>
     <t>СУРИНАМ</t>
   </si>
   <si>
@@ -2717,5567 +2722,5515 @@
     <t>EGY</t>
   </si>
   <si>
+    <t>СОЕДИНЕННОЕ КОРОЛЕВСТВО ВЕЛИКОБРИТАНИИ И СЕВЕРНОЙ ИРЛАНДИИ</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>ГЕРНСИ</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>GGY</t>
+  </si>
+  <si>
+    <t>ДЖЕРСИ</t>
+  </si>
+  <si>
+    <t>JE</t>
+  </si>
+  <si>
+    <t>JEY</t>
+  </si>
+  <si>
+    <t>ОСТРОВ МЭН</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>IMN</t>
+  </si>
+  <si>
+    <t>ТАНЗАНИЯ, ОБЪЕДИНЕННАЯ РЕСПУБЛИКА</t>
+  </si>
+  <si>
+    <t>Объединенная Республика Танзания</t>
+  </si>
+  <si>
+    <t>TZ</t>
+  </si>
+  <si>
+    <t>TZA</t>
+  </si>
+  <si>
+    <t>СОЕДИНЕННЫЕ ШТАТЫ</t>
+  </si>
+  <si>
+    <t>Соединенные Штаты Америки</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>ВИРГИНСКИЕ ОСТРОВА (США)</t>
+  </si>
+  <si>
+    <t>Виргинские острова Соединенных Штатов</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>БУРКИНА-ФАСО</t>
+  </si>
+  <si>
+    <t>BF</t>
+  </si>
+  <si>
+    <t>BFA</t>
+  </si>
+  <si>
+    <t>УРУГВАЙ</t>
+  </si>
+  <si>
+    <t>Восточная Республика Уругвай</t>
+  </si>
+  <si>
+    <t>UY</t>
+  </si>
+  <si>
+    <t>URY</t>
+  </si>
+  <si>
+    <t>УЗБЕКИСТАН</t>
+  </si>
+  <si>
+    <t>Республика Узбекистан</t>
+  </si>
+  <si>
+    <t>UZ</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>ВЕНЕСУЭЛА, БОЛИВАРИАНСКАЯ РЕСПУБЛИКА</t>
+  </si>
+  <si>
+    <t>Боливарианская Республика Венесуэла</t>
+  </si>
+  <si>
+    <t>VE</t>
+  </si>
+  <si>
+    <t>VEN</t>
+  </si>
+  <si>
+    <t>УОЛЛИС И ФУТУНА</t>
+  </si>
+  <si>
+    <t>WF</t>
+  </si>
+  <si>
+    <t>WLF</t>
+  </si>
+  <si>
+    <t>САМОА</t>
+  </si>
+  <si>
+    <t>Независимое Государство Самоа</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>ЙЕМЕН</t>
+  </si>
+  <si>
+    <t>Йеменская Республика</t>
+  </si>
+  <si>
+    <t>YE</t>
+  </si>
+  <si>
+    <t>YEM</t>
+  </si>
+  <si>
+    <t>ЗАМБИЯ</t>
+  </si>
+  <si>
+    <t>Республика Замбия</t>
+  </si>
+  <si>
+    <t>ZM</t>
+  </si>
+  <si>
+    <t>ZMB</t>
+  </si>
+  <si>
+    <t>АБХАЗИЯ</t>
+  </si>
+  <si>
+    <t>Республика Абхазия</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>ABH</t>
+  </si>
+  <si>
+    <t>ЮЖНАЯ ОСЕТИЯ</t>
+  </si>
+  <si>
+    <t>Республика Южная Осетия</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>OST</t>
+  </si>
+  <si>
+    <t>ДНР</t>
+  </si>
+  <si>
+    <t>Донецкая Народная Республика</t>
+  </si>
+  <si>
+    <t>DN</t>
+  </si>
+  <si>
+    <t>DNR</t>
+  </si>
+  <si>
+    <t>ЛНР</t>
+  </si>
+  <si>
+    <t>Луганская Народная Республика</t>
+  </si>
+  <si>
+    <t>LN</t>
+  </si>
+  <si>
+    <t>LNR</t>
+  </si>
+  <si>
+    <t>Краткое наименование (историческое / дата появления)</t>
+  </si>
+  <si>
+    <t>ДействуетС</t>
+  </si>
+  <si>
+    <t>ДействуетПо</t>
+  </si>
+  <si>
+    <t>Примечание</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>ЭЛАНДСКИЕ ОСТРОВА</t>
+  </si>
+  <si>
+    <t>01.05.2023</t>
+  </si>
+  <si>
+    <t>До изм. 30/2023 (введено 01.05.2023)</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>НИДЕРЛАНДЫ</t>
+  </si>
+  <si>
+    <t>01.10.2023</t>
+  </si>
+  <si>
+    <t>До изм. 32/2023 (введено 01.10.2023)</t>
+  </si>
+  <si>
+    <t>826</t>
+  </si>
+  <si>
     <t>СОЕДИНЕННОЕ КОРОЛЕВСТВО</t>
   </si>
   <si>
-    <t>Соединенное Королевство Великобритании и Северной Ирландии</t>
-  </si>
-  <si>
-    <t>GB</t>
-  </si>
-  <si>
-    <t>GBR</t>
-  </si>
-  <si>
-    <t>ГЕРНСИ</t>
-  </si>
-  <si>
-    <t>GG</t>
-  </si>
-  <si>
-    <t>GGY</t>
-  </si>
-  <si>
-    <t>ДЖЕРСИ</t>
-  </si>
-  <si>
-    <t>JE</t>
-  </si>
-  <si>
-    <t>JEY</t>
-  </si>
-  <si>
-    <t>ОСТРОВ МЭН</t>
-  </si>
-  <si>
-    <t>IM</t>
-  </si>
-  <si>
-    <t>IMN</t>
-  </si>
-  <si>
-    <t>ТАНЗАНИЯ, ОБЪЕДИНЕННАЯ РЕСПУБЛИКА</t>
-  </si>
-  <si>
-    <t>Объединенная Республика Танзания</t>
-  </si>
-  <si>
-    <t>TZ</t>
-  </si>
-  <si>
-    <t>TZA</t>
-  </si>
-  <si>
-    <t>СОЕДИНЕННЫЕ ШТАТЫ</t>
-  </si>
-  <si>
-    <t>Соединенные Штаты Америки</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>ВИРГИНСКИЕ ОСТРОВА (США)</t>
-  </si>
-  <si>
-    <t>Виргинские острова Соединенных Штатов</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>VIR</t>
-  </si>
-  <si>
-    <t>БУРКИНА-ФАСО</t>
-  </si>
-  <si>
-    <t>BF</t>
-  </si>
-  <si>
-    <t>BFA</t>
-  </si>
-  <si>
-    <t>УРУГВАЙ</t>
-  </si>
-  <si>
-    <t>Восточная Республика Уругвай</t>
-  </si>
-  <si>
-    <t>UY</t>
-  </si>
-  <si>
-    <t>URY</t>
-  </si>
-  <si>
-    <t>УЗБЕКИСТАН</t>
-  </si>
-  <si>
-    <t>Республика Узбекистан</t>
-  </si>
-  <si>
-    <t>UZ</t>
-  </si>
-  <si>
-    <t>UZB</t>
+    <t>862</t>
   </si>
   <si>
     <t>ВЕНЕСУЭЛА (БОЛИВАРИАНСКАЯ РЕСПУБЛИКА)</t>
   </si>
   <si>
-    <t>Боливарианская Республика Венесуэла</t>
-  </si>
-  <si>
-    <t>VE</t>
-  </si>
-  <si>
-    <t>VEN</t>
-  </si>
-  <si>
-    <t>УОЛЛИС И ФУТУНА</t>
-  </si>
-  <si>
-    <t>WF</t>
-  </si>
-  <si>
-    <t>WLF</t>
-  </si>
-  <si>
-    <t>САМОА</t>
-  </si>
-  <si>
-    <t>Независимое Государство Самоа</t>
-  </si>
-  <si>
-    <t>WS</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>ЙЕМЕН</t>
-  </si>
-  <si>
-    <t>Йеменская Республика</t>
-  </si>
-  <si>
-    <t>YE</t>
-  </si>
-  <si>
-    <t>YEM</t>
-  </si>
-  <si>
-    <t>ЗАМБИЯ</t>
-  </si>
-  <si>
-    <t>Республика Замбия</t>
-  </si>
-  <si>
-    <t>ZM</t>
-  </si>
-  <si>
-    <t>ZMB</t>
-  </si>
-  <si>
-    <t>АБХАЗИЯ</t>
-  </si>
-  <si>
-    <t>Республика Абхазия</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>ABH</t>
-  </si>
-  <si>
-    <t>ЮЖНАЯ ОСЕТИЯ</t>
-  </si>
-  <si>
-    <t>Республика Южная Осетия</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>OST</t>
-  </si>
-  <si>
-    <t>ЮЖНЫЙ СУДАН</t>
-  </si>
-  <si>
-    <t>Республика Южный Судан</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>SSD</t>
+    <t>01.08.2024</t>
+  </si>
+  <si>
+    <t>До изм. 33/2024 (введено 01.08.2024)</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>25.02.2022</t>
+  </si>
+  <si>
+    <t>Появление изм. 28/2022 (введено 25.02.2022); в актуальном файле сохраняется</t>
+  </si>
+  <si>
+    <t>898</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="single"/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:F258"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10.42578125" customWidth="true" style="0"/>
-    <col min="3" max="3" width="22" customWidth="true" style="0"/>
-    <col min="4" max="4" width="21.42578125" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10.85546875" customWidth="true" style="0"/>
-    <col min="6" max="6" width="10.85546875" customWidth="true" style="0"/>
-  </cols>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName=""/>
+  <dimension ref="A1:F260"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="23.25">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="0" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="0">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="0">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" s="0">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>22</v>
       </c>
       <c r="D10"/>
-      <c r="E10" t="s">
+      <c r="E10" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="0" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" s="0">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" s="0">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>31</v>
       </c>
       <c r="D12"/>
-      <c r="E12" t="s">
+      <c r="E12" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" s="0">
         <v>6</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
+    <row r="14">
+      <c r="A14" s="0">
         <v>7</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="0" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" s="0">
         <v>8</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>45</v>
       </c>
       <c r="D15"/>
-      <c r="E15" t="s">
+      <c r="E15" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
+    <row r="16">
+      <c r="A16" s="0">
         <v>9</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="0" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" s="0">
         <v>10</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="0" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
+    <row r="18">
+      <c r="A18" s="0">
         <v>11</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>59</v>
       </c>
       <c r="D18"/>
-      <c r="E18" t="s">
+      <c r="E18" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="0" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" s="0">
         <v>12</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="0" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" s="0">
         <v>13</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="0" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" s="0">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="0" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
+    <row r="22">
+      <c r="A22" s="0">
         <v>15</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="0" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
+    <row r="23">
+      <c r="A23" s="0">
         <v>16</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
+    <row r="24">
+      <c r="A24" s="0">
         <v>17</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="0" t="s">
         <v>88</v>
       </c>
       <c r="D24"/>
-      <c r="E24" t="s">
+      <c r="E24" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="0" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" s="0">
         <v>18</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="0" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" s="0">
         <v>19</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="0" t="s">
         <v>97</v>
       </c>
       <c r="D26"/>
-      <c r="E26" t="s">
+      <c r="E26" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="0" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
+    <row r="27">
+      <c r="A27" s="0">
         <v>20</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="0" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
+    <row r="28">
+      <c r="A28" s="0">
         <v>21</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="0" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
+    <row r="29">
+      <c r="A29" s="0">
         <v>22</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="0" t="s">
         <v>111</v>
       </c>
       <c r="D29"/>
-      <c r="E29" t="s">
+      <c r="E29" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="0" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
+    <row r="30">
+      <c r="A30" s="0">
         <v>23</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="0" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
+    <row r="31">
+      <c r="A31" s="0">
         <v>24</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="0" t="s">
         <v>120</v>
       </c>
       <c r="D31"/>
-      <c r="E31" t="s">
+      <c r="E31" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
+    <row r="32">
+      <c r="A32" s="0">
         <v>25</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="0" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
+    <row r="33">
+      <c r="A33" s="0">
         <v>26</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="0" t="s">
         <v>129</v>
       </c>
       <c r="D33"/>
-      <c r="E33" t="s">
+      <c r="E33" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="0" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
+    <row r="34">
+      <c r="A34" s="0">
         <v>27</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="0" t="s">
         <v>133</v>
       </c>
       <c r="D34"/>
-      <c r="E34" t="s">
+      <c r="E34" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="0" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
+    <row r="35">
+      <c r="A35" s="0">
         <v>28</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="0" t="s">
         <v>137</v>
       </c>
       <c r="D35"/>
-      <c r="E35" t="s">
+      <c r="E35" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="0" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
+    <row r="36">
+      <c r="A36" s="0">
         <v>29</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="0" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
+    <row r="37">
+      <c r="A37" s="0">
         <v>30</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="0" t="s">
         <v>146</v>
       </c>
       <c r="D37"/>
-      <c r="E37" t="s">
+      <c r="E37" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="0" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
+    <row r="38">
+      <c r="A38" s="0">
         <v>31</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="0">
         <v>100</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="0" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
+    <row r="39">
+      <c r="A39" s="0">
         <v>32</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="0">
         <v>104</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="0" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
+    <row r="40">
+      <c r="A40" s="0">
         <v>33</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="0">
         <v>108</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="0" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
+    <row r="41">
+      <c r="A41" s="0">
         <v>34</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="0">
         <v>112</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="0" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
+    <row r="42">
+      <c r="A42" s="0">
         <v>35</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="0">
         <v>116</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="0" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
+    <row r="43">
+      <c r="A43" s="0">
         <v>36</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="0">
         <v>120</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="0" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
+    <row r="44">
+      <c r="A44" s="0">
         <v>37</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="0">
         <v>124</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="0" t="s">
         <v>173</v>
       </c>
       <c r="D44"/>
-      <c r="E44" t="s">
+      <c r="E44" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="0" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
+    <row r="45">
+      <c r="A45" s="0">
         <v>38</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="0">
         <v>132</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="0" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
+    <row r="46">
+      <c r="A46" s="0">
         <v>39</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="0">
         <v>136</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="0" t="s">
         <v>180</v>
       </c>
       <c r="D46"/>
-      <c r="E46" t="s">
+      <c r="E46" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="0" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
+    <row r="47">
+      <c r="A47" s="0">
         <v>40</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="0">
         <v>140</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="0" t="s">
         <v>183</v>
       </c>
       <c r="D47"/>
-      <c r="E47" t="s">
+      <c r="E47" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="0" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
+    <row r="48">
+      <c r="A48" s="0">
         <v>41</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="0">
         <v>144</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="0" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
+    <row r="49">
+      <c r="A49" s="0">
         <v>42</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="0">
         <v>148</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="0" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
+    <row r="50">
+      <c r="A50" s="0">
         <v>43</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="0">
         <v>152</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="0" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
+    <row r="51">
+      <c r="A51" s="0">
         <v>44</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="0">
         <v>156</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="0" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
+    <row r="52">
+      <c r="A52" s="0">
         <v>45</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="0">
         <v>158</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="0" t="s">
         <v>202</v>
       </c>
       <c r="D52"/>
-      <c r="E52" t="s">
+      <c r="E52" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="0" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
+    <row r="53">
+      <c r="A53" s="0">
         <v>46</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="0">
         <v>162</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="0" t="s">
         <v>205</v>
       </c>
       <c r="D53"/>
-      <c r="E53" t="s">
+      <c r="E53" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="0" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
+    <row r="54">
+      <c r="A54" s="0">
         <v>47</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="0">
         <v>166</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="0" t="s">
         <v>208</v>
       </c>
       <c r="D54"/>
-      <c r="E54" t="s">
+      <c r="E54" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="0" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
+    <row r="55">
+      <c r="A55" s="0">
         <v>48</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="0">
         <v>170</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="0" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
+    <row r="56">
+      <c r="A56" s="0">
         <v>49</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="0">
         <v>174</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="0" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
+    <row r="57">
+      <c r="A57" s="0">
         <v>50</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="0">
         <v>175</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D57"/>
-      <c r="E57" t="s">
+      <c r="E57" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="0" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
+    <row r="58">
+      <c r="A58" s="0">
         <v>51</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="0">
         <v>178</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="0" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
+    <row r="59">
+      <c r="A59" s="0">
         <v>52</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="0">
         <v>180</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="0" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
+    <row r="60">
+      <c r="A60" s="0">
         <v>53</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="0">
         <v>184</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="0" t="s">
         <v>230</v>
       </c>
       <c r="D60"/>
-      <c r="E60" t="s">
+      <c r="E60" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="0" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
+    <row r="61">
+      <c r="A61" s="0">
         <v>54</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="0">
         <v>188</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="0" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
+    <row r="62">
+      <c r="A62" s="0">
         <v>55</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="0">
         <v>191</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="0" t="s">
         <v>238</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="0" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
+    <row r="63">
+      <c r="A63" s="0">
         <v>56</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="0">
         <v>192</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="0" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
+    <row r="64">
+      <c r="A64" s="0">
         <v>57</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="0">
         <v>196</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="0" t="s">
         <v>245</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="0" t="s">
         <v>246</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="0" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
+    <row r="65">
+      <c r="A65" s="0">
         <v>58</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="0">
         <v>203</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="0" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
+    <row r="66">
+      <c r="A66" s="0">
         <v>59</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="0">
         <v>204</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="0" t="s">
         <v>254</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="0" t="s">
         <v>255</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="0" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
+    <row r="67">
+      <c r="A67" s="0">
         <v>60</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="0">
         <v>208</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="0" t="s">
         <v>258</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="0" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
+    <row r="68">
+      <c r="A68" s="0">
         <v>61</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="0">
         <v>212</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="0" t="s">
         <v>261</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="0" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
+    <row r="69">
+      <c r="A69" s="0">
         <v>62</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="0">
         <v>214</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="0" t="s">
         <v>265</v>
       </c>
       <c r="D69"/>
-      <c r="E69" t="s">
+      <c r="E69" s="0" t="s">
         <v>266</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="0" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
+    <row r="70">
+      <c r="A70" s="0">
         <v>63</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="0">
         <v>218</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="0" t="s">
         <v>269</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="0" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
+    <row r="71">
+      <c r="A71" s="0">
         <v>64</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="0">
         <v>222</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="0" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
+    <row r="72">
+      <c r="A72" s="0">
         <v>65</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="0">
         <v>226</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="0" t="s">
         <v>276</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="0" t="s">
         <v>277</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="0" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
+    <row r="73">
+      <c r="A73" s="0">
         <v>66</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="0">
         <v>231</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="0" t="s">
         <v>280</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="0" t="s">
         <v>281</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="0" t="s">
         <v>282</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="0" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
+    <row r="74">
+      <c r="A74" s="0">
         <v>67</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="0">
         <v>232</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="0" t="s">
         <v>284</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="0" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
+    <row r="75">
+      <c r="A75" s="0">
         <v>68</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="0">
         <v>233</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="0" t="s">
         <v>288</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="0" t="s">
         <v>290</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="0" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
+    <row r="76">
+      <c r="A76" s="0">
         <v>69</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="0">
         <v>234</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="0" t="s">
         <v>292</v>
       </c>
       <c r="D76"/>
-      <c r="E76" t="s">
+      <c r="E76" s="0" t="s">
         <v>293</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="0" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
+    <row r="77">
+      <c r="A77" s="0">
         <v>70</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="0">
         <v>238</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="0" t="s">
         <v>295</v>
       </c>
       <c r="D77"/>
-      <c r="E77" t="s">
+      <c r="E77" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="0" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
+    <row r="78">
+      <c r="A78" s="0">
         <v>71</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="0">
         <v>239</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="0" t="s">
         <v>298</v>
       </c>
       <c r="D78"/>
-      <c r="E78" t="s">
+      <c r="E78" s="0" t="s">
         <v>299</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="0" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
+    <row r="79">
+      <c r="A79" s="0">
         <v>72</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="0">
         <v>242</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="0" t="s">
         <v>301</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="0" t="s">
         <v>303</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="0" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
+    <row r="80">
+      <c r="A80" s="0">
         <v>73</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="0">
         <v>246</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="0" t="s">
         <v>305</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="0" t="s">
         <v>306</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="0" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
+    <row r="81">
+      <c r="A81" s="0">
         <v>74</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="0">
         <v>248</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="0" t="s">
         <v>309</v>
       </c>
       <c r="D81"/>
-      <c r="E81" t="s">
+      <c r="E81" s="0" t="s">
         <v>310</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="0" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
+    <row r="82">
+      <c r="A82" s="0">
         <v>75</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="0">
         <v>250</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="0" t="s">
         <v>314</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="0" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
+    <row r="83">
+      <c r="A83" s="0">
         <v>76</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="0">
         <v>254</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="0" t="s">
         <v>316</v>
       </c>
       <c r="D83"/>
-      <c r="E83" t="s">
+      <c r="E83" s="0" t="s">
         <v>317</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="0" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
+    <row r="84">
+      <c r="A84" s="0">
         <v>77</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="0">
         <v>258</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="0" t="s">
         <v>319</v>
       </c>
       <c r="D84"/>
-      <c r="E84" t="s">
+      <c r="E84" s="0" t="s">
         <v>320</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="0" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
+    <row r="85">
+      <c r="A85" s="0">
         <v>78</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="0">
         <v>260</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="0" t="s">
         <v>322</v>
       </c>
       <c r="D85"/>
-      <c r="E85" t="s">
+      <c r="E85" s="0" t="s">
         <v>323</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="0" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
+    <row r="86">
+      <c r="A86" s="0">
         <v>79</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="0">
         <v>262</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="0" t="s">
         <v>325</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="0" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
+    <row r="87">
+      <c r="A87" s="0">
         <v>80</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="0">
         <v>266</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="0" t="s">
         <v>329</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="0" t="s">
         <v>330</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="0" t="s">
         <v>331</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="0" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
+    <row r="88">
+      <c r="A88" s="0">
         <v>81</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="0">
         <v>268</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="0" t="s">
         <v>333</v>
       </c>
       <c r="D88"/>
-      <c r="E88" t="s">
+      <c r="E88" s="0" t="s">
         <v>334</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="0" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
+    <row r="89">
+      <c r="A89" s="0">
         <v>82</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="0">
         <v>270</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="0" t="s">
         <v>336</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="0" t="s">
         <v>337</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="0" t="s">
         <v>338</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="0" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
+    <row r="90">
+      <c r="A90" s="0">
         <v>83</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="0">
         <v>275</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="0" t="s">
         <v>340</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="0" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
+    <row r="91">
+      <c r="A91" s="0">
         <v>84</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="0">
         <v>276</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="0" t="s">
         <v>344</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="0" t="s">
         <v>345</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="0" t="s">
         <v>346</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="0" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
+    <row r="92">
+      <c r="A92" s="0">
         <v>85</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="0">
         <v>288</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="0" t="s">
         <v>348</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="0" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
+    <row r="93">
+      <c r="A93" s="0">
         <v>86</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="0">
         <v>292</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="0" t="s">
         <v>352</v>
       </c>
       <c r="D93"/>
-      <c r="E93" t="s">
+      <c r="E93" s="0" t="s">
         <v>353</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="0" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
+    <row r="94">
+      <c r="A94" s="0">
         <v>87</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="0">
         <v>296</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="0" t="s">
         <v>355</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="0" t="s">
         <v>357</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="0" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
+    <row r="95">
+      <c r="A95" s="0">
         <v>88</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="0">
         <v>300</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="0" t="s">
         <v>360</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="0" t="s">
         <v>361</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="0" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
+    <row r="96">
+      <c r="A96" s="0">
         <v>89</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="0">
         <v>304</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="0" t="s">
         <v>363</v>
       </c>
       <c r="D96"/>
-      <c r="E96" t="s">
+      <c r="E96" s="0" t="s">
         <v>364</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="0" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
+    <row r="97">
+      <c r="A97" s="0">
         <v>90</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="0">
         <v>308</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="0" t="s">
         <v>366</v>
       </c>
       <c r="D97"/>
-      <c r="E97" t="s">
+      <c r="E97" s="0" t="s">
         <v>367</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="0" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
+    <row r="98">
+      <c r="A98" s="0">
         <v>91</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="0">
         <v>312</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="0" t="s">
         <v>369</v>
       </c>
       <c r="D98"/>
-      <c r="E98" t="s">
+      <c r="E98" s="0" t="s">
         <v>370</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="0" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
+    <row r="99">
+      <c r="A99" s="0">
         <v>92</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="0">
         <v>316</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="0" t="s">
         <v>372</v>
       </c>
       <c r="D99"/>
-      <c r="E99" t="s">
+      <c r="E99" s="0" t="s">
         <v>373</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="0" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
+    <row r="100">
+      <c r="A100" s="0">
         <v>93</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="0">
         <v>320</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="0" t="s">
         <v>375</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="0" t="s">
         <v>376</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="0" t="s">
         <v>377</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="0" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
+    <row r="101">
+      <c r="A101" s="0">
         <v>94</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="0">
         <v>324</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="0" t="s">
         <v>380</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="0" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" s="0">
         <v>95</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="0">
         <v>328</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="0" t="s">
         <v>383</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="0" t="s">
         <v>384</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="0" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" s="0">
         <v>96</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="0">
         <v>332</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="0" t="s">
         <v>387</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="0" t="s">
         <v>388</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="0" t="s">
         <v>389</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="0" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
+    <row r="104">
+      <c r="A104" s="0">
         <v>97</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="0">
         <v>334</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="0" t="s">
         <v>391</v>
       </c>
       <c r="D104"/>
-      <c r="E104" t="s">
+      <c r="E104" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="0" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
+    <row r="105">
+      <c r="A105" s="0">
         <v>98</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="0">
         <v>336</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="0" t="s">
         <v>394</v>
       </c>
       <c r="D105"/>
-      <c r="E105" t="s">
+      <c r="E105" s="0" t="s">
         <v>395</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="0" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
+    <row r="106">
+      <c r="A106" s="0">
         <v>99</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="0">
         <v>340</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="0" t="s">
         <v>397</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="0" t="s">
         <v>398</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="0" t="s">
         <v>399</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="0" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
+    <row r="107">
+      <c r="A107" s="0">
         <v>100</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="0">
         <v>344</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="0" t="s">
         <v>401</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="0" t="s">
         <v>402</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="0" t="s">
         <v>403</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="0" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
+    <row r="108">
+      <c r="A108" s="0">
         <v>101</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="0">
         <v>348</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="0" t="s">
         <v>405</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="0" t="s">
         <v>406</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="0" t="s">
         <v>407</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="0" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
+    <row r="109">
+      <c r="A109" s="0">
         <v>102</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="0">
         <v>352</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109"/>
+      <c r="E109" s="0" t="s">
         <v>410</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" s="0" t="s">
         <v>411</v>
       </c>
-      <c r="F109" t="s">
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>103</v>
+      </c>
+      <c r="B110" s="0">
+        <v>356</v>
+      </c>
+      <c r="C110" s="0" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>103</v>
-      </c>
-      <c r="B110">
-        <v>356</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="D110" s="0" t="s">
         <v>413</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" s="0" t="s">
         <v>414</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" s="0" t="s">
         <v>415</v>
       </c>
-      <c r="F110" t="s">
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>104</v>
+      </c>
+      <c r="B111" s="0">
+        <v>360</v>
+      </c>
+      <c r="C111" s="0" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>104</v>
-      </c>
-      <c r="B111">
-        <v>360</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="D111" s="0" t="s">
         <v>417</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" s="0" t="s">
         <v>418</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F111" t="s">
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>105</v>
+      </c>
+      <c r="B112" s="0">
+        <v>364</v>
+      </c>
+      <c r="C112" s="0" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>105</v>
-      </c>
-      <c r="B112">
-        <v>364</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="D112" s="0" t="s">
         <v>421</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" s="0" t="s">
         <v>422</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" s="0" t="s">
         <v>423</v>
       </c>
-      <c r="F112" t="s">
+    </row>
+    <row r="113">
+      <c r="A113" s="0">
+        <v>106</v>
+      </c>
+      <c r="B113" s="0">
+        <v>368</v>
+      </c>
+      <c r="C113" s="0" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>106</v>
-      </c>
-      <c r="B113">
-        <v>368</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="D113" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" s="0" t="s">
         <v>426</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" s="0" t="s">
         <v>427</v>
       </c>
-      <c r="F113" t="s">
+    </row>
+    <row r="114">
+      <c r="A114" s="0">
+        <v>107</v>
+      </c>
+      <c r="B114" s="0">
+        <v>372</v>
+      </c>
+      <c r="C114" s="0" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>107</v>
-      </c>
-      <c r="B114">
-        <v>372</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="D114"/>
+      <c r="E114" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="D114"/>
-      <c r="E114" t="s">
+      <c r="F114" s="0" t="s">
         <v>430</v>
       </c>
-      <c r="F114" t="s">
+    </row>
+    <row r="115">
+      <c r="A115" s="0">
+        <v>108</v>
+      </c>
+      <c r="B115" s="0">
+        <v>376</v>
+      </c>
+      <c r="C115" s="0" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>108</v>
-      </c>
-      <c r="B115">
-        <v>376</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="D115" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" s="0" t="s">
         <v>434</v>
       </c>
-      <c r="F115" t="s">
+    </row>
+    <row r="116">
+      <c r="A116" s="0">
+        <v>109</v>
+      </c>
+      <c r="B116" s="0">
+        <v>380</v>
+      </c>
+      <c r="C116" s="0" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>109</v>
-      </c>
-      <c r="B116">
-        <v>380</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="D116" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" s="0" t="s">
         <v>437</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" s="0" t="s">
         <v>438</v>
       </c>
-      <c r="F116" t="s">
+    </row>
+    <row r="117">
+      <c r="A117" s="0">
+        <v>110</v>
+      </c>
+      <c r="B117" s="0">
+        <v>384</v>
+      </c>
+      <c r="C117" s="0" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>110</v>
-      </c>
-      <c r="B117">
-        <v>384</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="D117" s="0" t="s">
         <v>440</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" s="0" t="s">
         <v>442</v>
       </c>
-      <c r="F117" t="s">
+    </row>
+    <row r="118">
+      <c r="A118" s="0">
+        <v>111</v>
+      </c>
+      <c r="B118" s="0">
+        <v>388</v>
+      </c>
+      <c r="C118" s="0" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>111</v>
-      </c>
-      <c r="B118">
-        <v>388</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="D118"/>
+      <c r="E118" s="0" t="s">
         <v>444</v>
       </c>
-      <c r="D118"/>
-      <c r="E118" t="s">
+      <c r="F118" s="0" t="s">
         <v>445</v>
       </c>
-      <c r="F118" t="s">
+    </row>
+    <row r="119">
+      <c r="A119" s="0">
+        <v>112</v>
+      </c>
+      <c r="B119" s="0">
+        <v>392</v>
+      </c>
+      <c r="C119" s="0" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>112</v>
-      </c>
-      <c r="B119">
-        <v>392</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="D119"/>
+      <c r="E119" s="0" t="s">
         <v>447</v>
       </c>
-      <c r="D119"/>
-      <c r="E119" t="s">
+      <c r="F119" s="0" t="s">
         <v>448</v>
       </c>
-      <c r="F119" t="s">
+    </row>
+    <row r="120">
+      <c r="A120" s="0">
+        <v>113</v>
+      </c>
+      <c r="B120" s="0">
+        <v>398</v>
+      </c>
+      <c r="C120" s="0" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>113</v>
-      </c>
-      <c r="B120">
-        <v>398</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="D120" s="0" t="s">
         <v>450</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" s="0" t="s">
         <v>451</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="F120" t="s">
+    </row>
+    <row r="121">
+      <c r="A121" s="0">
+        <v>114</v>
+      </c>
+      <c r="B121" s="0">
+        <v>400</v>
+      </c>
+      <c r="C121" s="0" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>114</v>
-      </c>
-      <c r="B121">
-        <v>400</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="D121" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="F121" t="s">
+    </row>
+    <row r="122">
+      <c r="A122" s="0">
+        <v>115</v>
+      </c>
+      <c r="B122" s="0">
+        <v>404</v>
+      </c>
+      <c r="C122" s="0" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>115</v>
-      </c>
-      <c r="B122">
-        <v>404</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="D122" s="0" t="s">
         <v>458</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" s="0" t="s">
         <v>459</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" s="0" t="s">
         <v>460</v>
       </c>
-      <c r="F122" t="s">
+    </row>
+    <row r="123">
+      <c r="A123" s="0">
+        <v>116</v>
+      </c>
+      <c r="B123" s="0">
+        <v>408</v>
+      </c>
+      <c r="C123" s="0" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>116</v>
-      </c>
-      <c r="B123">
-        <v>408</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="D123" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" s="0" t="s">
         <v>463</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" s="0" t="s">
         <v>464</v>
       </c>
-      <c r="F123" t="s">
+    </row>
+    <row r="124">
+      <c r="A124" s="0">
+        <v>117</v>
+      </c>
+      <c r="B124" s="0">
+        <v>410</v>
+      </c>
+      <c r="C124" s="0" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>117</v>
-      </c>
-      <c r="B124">
-        <v>410</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="D124" s="0" t="s">
         <v>466</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" s="0" t="s">
         <v>467</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" s="0" t="s">
         <v>468</v>
       </c>
-      <c r="F124" t="s">
+    </row>
+    <row r="125">
+      <c r="A125" s="0">
+        <v>118</v>
+      </c>
+      <c r="B125" s="0">
+        <v>414</v>
+      </c>
+      <c r="C125" s="0" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>118</v>
-      </c>
-      <c r="B125">
-        <v>414</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="D125" s="0" t="s">
         <v>470</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" s="0" t="s">
         <v>471</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="F125" t="s">
+    </row>
+    <row r="126">
+      <c r="A126" s="0">
+        <v>119</v>
+      </c>
+      <c r="B126" s="0">
+        <v>417</v>
+      </c>
+      <c r="C126" s="0" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>119</v>
-      </c>
-      <c r="B126">
-        <v>417</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="D126" s="0" t="s">
         <v>474</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" s="0" t="s">
         <v>476</v>
       </c>
-      <c r="F126" t="s">
+    </row>
+    <row r="127">
+      <c r="A127" s="0">
+        <v>120</v>
+      </c>
+      <c r="B127" s="0">
+        <v>418</v>
+      </c>
+      <c r="C127" s="0" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>120</v>
-      </c>
-      <c r="B127">
-        <v>418</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="D127"/>
+      <c r="E127" s="0" t="s">
         <v>478</v>
       </c>
-      <c r="D127"/>
-      <c r="E127" t="s">
+      <c r="F127" s="0" t="s">
         <v>479</v>
       </c>
-      <c r="F127" t="s">
+    </row>
+    <row r="128">
+      <c r="A128" s="0">
+        <v>121</v>
+      </c>
+      <c r="B128" s="0">
+        <v>422</v>
+      </c>
+      <c r="C128" s="0" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>121</v>
-      </c>
-      <c r="B128">
-        <v>422</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="D128" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" s="0" t="s">
         <v>483</v>
       </c>
-      <c r="F128" t="s">
+    </row>
+    <row r="129">
+      <c r="A129" s="0">
+        <v>122</v>
+      </c>
+      <c r="B129" s="0">
+        <v>426</v>
+      </c>
+      <c r="C129" s="0" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>122</v>
-      </c>
-      <c r="B129">
-        <v>426</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="D129" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" s="0" t="s">
         <v>486</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" s="0" t="s">
         <v>487</v>
       </c>
-      <c r="F129" t="s">
+    </row>
+    <row r="130">
+      <c r="A130" s="0">
+        <v>123</v>
+      </c>
+      <c r="B130" s="0">
+        <v>428</v>
+      </c>
+      <c r="C130" s="0" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>123</v>
-      </c>
-      <c r="B130">
-        <v>428</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="D130" s="0" t="s">
         <v>489</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" s="0" t="s">
         <v>490</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" s="0" t="s">
         <v>491</v>
       </c>
-      <c r="F130" t="s">
+    </row>
+    <row r="131">
+      <c r="A131" s="0">
+        <v>124</v>
+      </c>
+      <c r="B131" s="0">
+        <v>430</v>
+      </c>
+      <c r="C131" s="0" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>124</v>
-      </c>
-      <c r="B131">
-        <v>430</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="D131" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" s="0" t="s">
         <v>494</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" s="0" t="s">
         <v>495</v>
       </c>
-      <c r="F131" t="s">
+    </row>
+    <row r="132">
+      <c r="A132" s="0">
+        <v>125</v>
+      </c>
+      <c r="B132" s="0">
+        <v>434</v>
+      </c>
+      <c r="C132" s="0" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>125</v>
-      </c>
-      <c r="B132">
-        <v>434</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="D132" s="0" t="s">
         <v>497</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" s="0" t="s">
         <v>498</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" s="0" t="s">
         <v>499</v>
       </c>
-      <c r="F132" t="s">
+    </row>
+    <row r="133">
+      <c r="A133" s="0">
+        <v>126</v>
+      </c>
+      <c r="B133" s="0">
+        <v>438</v>
+      </c>
+      <c r="C133" s="0" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>126</v>
-      </c>
-      <c r="B133">
-        <v>438</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="D133" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="F133" t="s">
+    </row>
+    <row r="134">
+      <c r="A134" s="0">
+        <v>127</v>
+      </c>
+      <c r="B134" s="0">
+        <v>440</v>
+      </c>
+      <c r="C134" s="0" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>127</v>
-      </c>
-      <c r="B134">
-        <v>440</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="D134" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" s="0" t="s">
         <v>507</v>
       </c>
-      <c r="F134" t="s">
+    </row>
+    <row r="135">
+      <c r="A135" s="0">
+        <v>128</v>
+      </c>
+      <c r="B135" s="0">
+        <v>442</v>
+      </c>
+      <c r="C135" s="0" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>128</v>
-      </c>
-      <c r="B135">
-        <v>442</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="D135" s="0" t="s">
         <v>509</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="F135" t="s">
+    </row>
+    <row r="136">
+      <c r="A136" s="0">
+        <v>129</v>
+      </c>
+      <c r="B136" s="0">
+        <v>446</v>
+      </c>
+      <c r="C136" s="0" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>129</v>
-      </c>
-      <c r="B136">
-        <v>446</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="D136" s="0" t="s">
         <v>513</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" s="0" t="s">
         <v>514</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" s="0" t="s">
         <v>515</v>
       </c>
-      <c r="F136" t="s">
+    </row>
+    <row r="137">
+      <c r="A137" s="0">
+        <v>130</v>
+      </c>
+      <c r="B137" s="0">
+        <v>450</v>
+      </c>
+      <c r="C137" s="0" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>130</v>
-      </c>
-      <c r="B137">
-        <v>450</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="D137" s="0" t="s">
         <v>517</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" s="0" t="s">
         <v>518</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" s="0" t="s">
         <v>519</v>
       </c>
-      <c r="F137" t="s">
+    </row>
+    <row r="138">
+      <c r="A138" s="0">
+        <v>131</v>
+      </c>
+      <c r="B138" s="0">
+        <v>454</v>
+      </c>
+      <c r="C138" s="0" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>131</v>
-      </c>
-      <c r="B138">
-        <v>454</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="D138" s="0" t="s">
         <v>521</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" s="0" t="s">
         <v>522</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" s="0" t="s">
         <v>523</v>
       </c>
-      <c r="F138" t="s">
+    </row>
+    <row r="139">
+      <c r="A139" s="0">
+        <v>132</v>
+      </c>
+      <c r="B139" s="0">
+        <v>458</v>
+      </c>
+      <c r="C139" s="0" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>132</v>
-      </c>
-      <c r="B139">
-        <v>458</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="D139"/>
+      <c r="E139" s="0" t="s">
         <v>525</v>
       </c>
-      <c r="D139"/>
-      <c r="E139" t="s">
+      <c r="F139" s="0" t="s">
         <v>526</v>
       </c>
-      <c r="F139" t="s">
+    </row>
+    <row r="140">
+      <c r="A140" s="0">
+        <v>133</v>
+      </c>
+      <c r="B140" s="0">
+        <v>462</v>
+      </c>
+      <c r="C140" s="0" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>133</v>
-      </c>
-      <c r="B140">
-        <v>462</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="D140" s="0" t="s">
         <v>528</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" s="0" t="s">
         <v>529</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" s="0" t="s">
         <v>530</v>
       </c>
-      <c r="F140" t="s">
+    </row>
+    <row r="141">
+      <c r="A141" s="0">
+        <v>134</v>
+      </c>
+      <c r="B141" s="0">
+        <v>466</v>
+      </c>
+      <c r="C141" s="0" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>134</v>
-      </c>
-      <c r="B141">
-        <v>466</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="D141" s="0" t="s">
         <v>532</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" s="0" t="s">
         <v>533</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" s="0" t="s">
         <v>534</v>
       </c>
-      <c r="F141" t="s">
+    </row>
+    <row r="142">
+      <c r="A142" s="0">
+        <v>135</v>
+      </c>
+      <c r="B142" s="0">
+        <v>470</v>
+      </c>
+      <c r="C142" s="0" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>135</v>
-      </c>
-      <c r="B142">
-        <v>470</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="D142" s="0" t="s">
         <v>536</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" s="0" t="s">
         <v>537</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" s="0" t="s">
         <v>538</v>
       </c>
-      <c r="F142" t="s">
+    </row>
+    <row r="143">
+      <c r="A143" s="0">
+        <v>136</v>
+      </c>
+      <c r="B143" s="0">
+        <v>474</v>
+      </c>
+      <c r="C143" s="0" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>136</v>
-      </c>
-      <c r="B143">
-        <v>474</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="D143"/>
+      <c r="E143" s="0" t="s">
         <v>540</v>
       </c>
-      <c r="D143"/>
-      <c r="E143" t="s">
+      <c r="F143" s="0" t="s">
         <v>541</v>
       </c>
-      <c r="F143" t="s">
+    </row>
+    <row r="144">
+      <c r="A144" s="0">
+        <v>137</v>
+      </c>
+      <c r="B144" s="0">
+        <v>478</v>
+      </c>
+      <c r="C144" s="0" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>137</v>
-      </c>
-      <c r="B144">
-        <v>478</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="D144" s="0" t="s">
         <v>543</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" s="0" t="s">
         <v>544</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" s="0" t="s">
         <v>545</v>
       </c>
-      <c r="F144" t="s">
+    </row>
+    <row r="145">
+      <c r="A145" s="0">
+        <v>138</v>
+      </c>
+      <c r="B145" s="0">
+        <v>480</v>
+      </c>
+      <c r="C145" s="0" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>138</v>
-      </c>
-      <c r="B145">
-        <v>480</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="D145" s="0" t="s">
         <v>547</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" s="0" t="s">
         <v>548</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" s="0" t="s">
         <v>549</v>
       </c>
-      <c r="F145" t="s">
+    </row>
+    <row r="146">
+      <c r="A146" s="0">
+        <v>139</v>
+      </c>
+      <c r="B146" s="0">
+        <v>484</v>
+      </c>
+      <c r="C146" s="0" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>139</v>
-      </c>
-      <c r="B146">
-        <v>484</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="D146" s="0" t="s">
         <v>551</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" s="0" t="s">
         <v>552</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" s="0" t="s">
         <v>553</v>
       </c>
-      <c r="F146" t="s">
+    </row>
+    <row r="147">
+      <c r="A147" s="0">
+        <v>140</v>
+      </c>
+      <c r="B147" s="0">
+        <v>492</v>
+      </c>
+      <c r="C147" s="0" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>140</v>
-      </c>
-      <c r="B147">
-        <v>492</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D147" s="0" t="s">
         <v>555</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="F147" t="s">
+    </row>
+    <row r="148">
+      <c r="A148" s="0">
+        <v>141</v>
+      </c>
+      <c r="B148" s="0">
+        <v>496</v>
+      </c>
+      <c r="C148" s="0" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>141</v>
-      </c>
-      <c r="B148">
-        <v>496</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="D148"/>
+      <c r="E148" s="0" t="s">
         <v>559</v>
       </c>
-      <c r="D148"/>
-      <c r="E148" t="s">
+      <c r="F148" s="0" t="s">
         <v>560</v>
       </c>
-      <c r="F148" t="s">
+    </row>
+    <row r="149">
+      <c r="A149" s="0">
+        <v>142</v>
+      </c>
+      <c r="B149" s="0">
+        <v>498</v>
+      </c>
+      <c r="C149" s="0" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>142</v>
-      </c>
-      <c r="B149">
-        <v>498</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="D149" s="0" t="s">
         <v>562</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" s="0" t="s">
         <v>563</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" s="0" t="s">
         <v>564</v>
       </c>
-      <c r="F149" t="s">
+    </row>
+    <row r="150">
+      <c r="A150" s="0">
+        <v>143</v>
+      </c>
+      <c r="B150" s="0">
+        <v>499</v>
+      </c>
+      <c r="C150" s="0" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>143</v>
-      </c>
-      <c r="B150">
-        <v>499</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="D150"/>
+      <c r="E150" s="0" t="s">
         <v>566</v>
       </c>
-      <c r="D150"/>
-      <c r="E150" t="s">
+      <c r="F150" s="0" t="s">
         <v>567</v>
       </c>
-      <c r="F150" t="s">
+    </row>
+    <row r="151">
+      <c r="A151" s="0">
+        <v>144</v>
+      </c>
+      <c r="B151" s="0">
+        <v>500</v>
+      </c>
+      <c r="C151" s="0" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>144</v>
-      </c>
-      <c r="B151">
-        <v>500</v>
-      </c>
-      <c r="C151" t="s">
+      <c r="D151"/>
+      <c r="E151" s="0" t="s">
         <v>569</v>
       </c>
-      <c r="D151"/>
-      <c r="E151" t="s">
+      <c r="F151" s="0" t="s">
         <v>570</v>
       </c>
-      <c r="F151" t="s">
+    </row>
+    <row r="152">
+      <c r="A152" s="0">
+        <v>145</v>
+      </c>
+      <c r="B152" s="0">
+        <v>504</v>
+      </c>
+      <c r="C152" s="0" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>145</v>
-      </c>
-      <c r="B152">
-        <v>504</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="D152" s="0" t="s">
         <v>572</v>
       </c>
-      <c r="D152" t="s">
+      <c r="E152" s="0" t="s">
         <v>573</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" s="0" t="s">
         <v>574</v>
       </c>
-      <c r="F152" t="s">
+    </row>
+    <row r="153">
+      <c r="A153" s="0">
+        <v>146</v>
+      </c>
+      <c r="B153" s="0">
+        <v>508</v>
+      </c>
+      <c r="C153" s="0" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>146</v>
-      </c>
-      <c r="B153">
-        <v>508</v>
-      </c>
-      <c r="C153" t="s">
+      <c r="D153" s="0" t="s">
         <v>576</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" s="0" t="s">
         <v>577</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" s="0" t="s">
         <v>578</v>
       </c>
-      <c r="F153" t="s">
+    </row>
+    <row r="154">
+      <c r="A154" s="0">
+        <v>147</v>
+      </c>
+      <c r="B154" s="0">
+        <v>512</v>
+      </c>
+      <c r="C154" s="0" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>147</v>
-      </c>
-      <c r="B154">
-        <v>512</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="D154" s="0" t="s">
         <v>580</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" s="0" t="s">
         <v>581</v>
       </c>
-      <c r="E154" t="s">
+      <c r="F154" s="0" t="s">
         <v>582</v>
       </c>
-      <c r="F154" t="s">
+    </row>
+    <row r="155">
+      <c r="A155" s="0">
+        <v>148</v>
+      </c>
+      <c r="B155" s="0">
+        <v>516</v>
+      </c>
+      <c r="C155" s="0" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>148</v>
-      </c>
-      <c r="B155">
-        <v>516</v>
-      </c>
-      <c r="C155" t="s">
+      <c r="D155" s="0" t="s">
         <v>584</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" s="0" t="s">
         <v>585</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" s="0" t="s">
         <v>586</v>
       </c>
-      <c r="F155" t="s">
+    </row>
+    <row r="156">
+      <c r="A156" s="0">
+        <v>149</v>
+      </c>
+      <c r="B156" s="0">
+        <v>520</v>
+      </c>
+      <c r="C156" s="0" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>149</v>
-      </c>
-      <c r="B156">
-        <v>520</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="D156" s="0" t="s">
         <v>588</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" s="0" t="s">
         <v>589</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" s="0" t="s">
         <v>590</v>
       </c>
-      <c r="F156" t="s">
+    </row>
+    <row r="157">
+      <c r="A157" s="0">
+        <v>150</v>
+      </c>
+      <c r="B157" s="0">
+        <v>524</v>
+      </c>
+      <c r="C157" s="0" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>150</v>
-      </c>
-      <c r="B157">
-        <v>524</v>
-      </c>
-      <c r="C157" t="s">
+      <c r="D157"/>
+      <c r="E157" s="0" t="s">
         <v>592</v>
       </c>
-      <c r="D157"/>
-      <c r="E157" t="s">
+      <c r="F157" s="0" t="s">
         <v>593</v>
       </c>
-      <c r="F157" t="s">
+    </row>
+    <row r="158">
+      <c r="A158" s="0">
+        <v>151</v>
+      </c>
+      <c r="B158" s="0">
+        <v>528</v>
+      </c>
+      <c r="C158" s="0" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>151</v>
-      </c>
-      <c r="B158">
-        <v>528</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="D158" s="0" t="s">
         <v>595</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" s="0" t="s">
         <v>596</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" s="0" t="s">
         <v>597</v>
       </c>
-      <c r="F158" t="s">
+    </row>
+    <row r="159">
+      <c r="A159" s="0">
+        <v>152</v>
+      </c>
+      <c r="B159" s="0">
+        <v>531</v>
+      </c>
+      <c r="C159" s="0" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>152</v>
-      </c>
-      <c r="B159">
-        <v>531</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="D159"/>
+      <c r="E159" s="0" t="s">
         <v>599</v>
       </c>
-      <c r="D159"/>
-      <c r="E159" t="s">
+      <c r="F159" s="0" t="s">
         <v>600</v>
       </c>
-      <c r="F159" t="s">
+    </row>
+    <row r="160">
+      <c r="A160" s="0">
+        <v>153</v>
+      </c>
+      <c r="B160" s="0">
+        <v>533</v>
+      </c>
+      <c r="C160" s="0" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>153</v>
-      </c>
-      <c r="B160">
-        <v>533</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="D160"/>
+      <c r="E160" s="0" t="s">
         <v>602</v>
       </c>
-      <c r="D160"/>
-      <c r="E160" t="s">
+      <c r="F160" s="0" t="s">
         <v>603</v>
       </c>
-      <c r="F160" t="s">
+    </row>
+    <row r="161">
+      <c r="A161" s="0">
+        <v>154</v>
+      </c>
+      <c r="B161" s="0">
+        <v>534</v>
+      </c>
+      <c r="C161" s="0" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>154</v>
-      </c>
-      <c r="B161">
-        <v>534</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="D161"/>
+      <c r="E161" s="0" t="s">
         <v>605</v>
       </c>
-      <c r="D161"/>
-      <c r="E161" t="s">
+      <c r="F161" s="0" t="s">
         <v>606</v>
       </c>
-      <c r="F161" t="s">
+    </row>
+    <row r="162">
+      <c r="A162" s="0">
+        <v>155</v>
+      </c>
+      <c r="B162" s="0">
+        <v>535</v>
+      </c>
+      <c r="C162" s="0" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>155</v>
-      </c>
-      <c r="B162">
-        <v>535</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="D162"/>
+      <c r="E162" s="0" t="s">
         <v>608</v>
       </c>
-      <c r="D162"/>
-      <c r="E162" t="s">
+      <c r="F162" s="0" t="s">
         <v>609</v>
       </c>
-      <c r="F162" t="s">
+    </row>
+    <row r="163">
+      <c r="A163" s="0">
+        <v>156</v>
+      </c>
+      <c r="B163" s="0">
+        <v>540</v>
+      </c>
+      <c r="C163" s="0" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>156</v>
-      </c>
-      <c r="B163">
-        <v>540</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="D163"/>
+      <c r="E163" s="0" t="s">
         <v>611</v>
       </c>
-      <c r="D163"/>
-      <c r="E163" t="s">
+      <c r="F163" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="F163" t="s">
+    </row>
+    <row r="164">
+      <c r="A164" s="0">
+        <v>157</v>
+      </c>
+      <c r="B164" s="0">
+        <v>548</v>
+      </c>
+      <c r="C164" s="0" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>157</v>
-      </c>
-      <c r="B164">
-        <v>548</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="D164" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" s="0" t="s">
         <v>615</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" s="0" t="s">
         <v>616</v>
       </c>
-      <c r="F164" t="s">
+    </row>
+    <row r="165">
+      <c r="A165" s="0">
+        <v>158</v>
+      </c>
+      <c r="B165" s="0">
+        <v>554</v>
+      </c>
+      <c r="C165" s="0" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>158</v>
-      </c>
-      <c r="B165">
-        <v>554</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="D165"/>
+      <c r="E165" s="0" t="s">
         <v>618</v>
       </c>
-      <c r="D165"/>
-      <c r="E165" t="s">
+      <c r="F165" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="F165" t="s">
+    </row>
+    <row r="166">
+      <c r="A166" s="0">
+        <v>159</v>
+      </c>
+      <c r="B166" s="0">
+        <v>558</v>
+      </c>
+      <c r="C166" s="0" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>159</v>
-      </c>
-      <c r="B166">
-        <v>558</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="D166" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" s="0" t="s">
         <v>623</v>
       </c>
-      <c r="F166" t="s">
+    </row>
+    <row r="167">
+      <c r="A167" s="0">
+        <v>160</v>
+      </c>
+      <c r="B167" s="0">
+        <v>562</v>
+      </c>
+      <c r="C167" s="0" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>160</v>
-      </c>
-      <c r="B167">
-        <v>562</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="D167" s="0" t="s">
         <v>625</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" s="0" t="s">
         <v>626</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" s="0" t="s">
         <v>627</v>
       </c>
-      <c r="F167" t="s">
+    </row>
+    <row r="168">
+      <c r="A168" s="0">
+        <v>161</v>
+      </c>
+      <c r="B168" s="0">
+        <v>566</v>
+      </c>
+      <c r="C168" s="0" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>161</v>
-      </c>
-      <c r="B168">
-        <v>566</v>
-      </c>
-      <c r="C168" t="s">
+      <c r="D168" s="0" t="s">
         <v>629</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" s="0" t="s">
         <v>630</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" s="0" t="s">
         <v>631</v>
       </c>
-      <c r="F168" t="s">
+    </row>
+    <row r="169">
+      <c r="A169" s="0">
+        <v>162</v>
+      </c>
+      <c r="B169" s="0">
+        <v>570</v>
+      </c>
+      <c r="C169" s="0" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>162</v>
-      </c>
-      <c r="B169">
-        <v>570</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="D169" s="0" t="s">
         <v>633</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" s="0" t="s">
         <v>634</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" s="0" t="s">
         <v>635</v>
       </c>
-      <c r="F169" t="s">
+    </row>
+    <row r="170">
+      <c r="A170" s="0">
+        <v>163</v>
+      </c>
+      <c r="B170" s="0">
+        <v>574</v>
+      </c>
+      <c r="C170" s="0" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>163</v>
-      </c>
-      <c r="B170">
-        <v>574</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="D170"/>
+      <c r="E170" s="0" t="s">
         <v>637</v>
       </c>
-      <c r="D170"/>
-      <c r="E170" t="s">
+      <c r="F170" s="0" t="s">
         <v>638</v>
       </c>
-      <c r="F170" t="s">
+    </row>
+    <row r="171">
+      <c r="A171" s="0">
+        <v>164</v>
+      </c>
+      <c r="B171" s="0">
+        <v>578</v>
+      </c>
+      <c r="C171" s="0" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>164</v>
-      </c>
-      <c r="B171">
-        <v>578</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="D171" s="0" t="s">
         <v>640</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" s="0" t="s">
         <v>641</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" s="0" t="s">
         <v>642</v>
       </c>
-      <c r="F171" t="s">
+    </row>
+    <row r="172">
+      <c r="A172" s="0">
+        <v>165</v>
+      </c>
+      <c r="B172" s="0">
+        <v>580</v>
+      </c>
+      <c r="C172" s="0" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>165</v>
-      </c>
-      <c r="B172">
-        <v>580</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="D172" s="0" t="s">
         <v>644</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" s="0" t="s">
         <v>645</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" s="0" t="s">
         <v>646</v>
       </c>
-      <c r="F172" t="s">
+    </row>
+    <row r="173">
+      <c r="A173" s="0">
+        <v>166</v>
+      </c>
+      <c r="B173" s="0">
+        <v>581</v>
+      </c>
+      <c r="C173" s="0" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>166</v>
-      </c>
-      <c r="B173">
-        <v>581</v>
-      </c>
-      <c r="C173" t="s">
+      <c r="D173"/>
+      <c r="E173" s="0" t="s">
         <v>648</v>
       </c>
-      <c r="D173"/>
-      <c r="E173" t="s">
+      <c r="F173" s="0" t="s">
         <v>649</v>
       </c>
-      <c r="F173" t="s">
+    </row>
+    <row r="174">
+      <c r="A174" s="0">
+        <v>167</v>
+      </c>
+      <c r="B174" s="0">
+        <v>583</v>
+      </c>
+      <c r="C174" s="0" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174">
-        <v>167</v>
-      </c>
-      <c r="B174">
-        <v>583</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="D174" s="0" t="s">
         <v>651</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" s="0" t="s">
         <v>652</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="F174" t="s">
+    </row>
+    <row r="175">
+      <c r="A175" s="0">
+        <v>168</v>
+      </c>
+      <c r="B175" s="0">
+        <v>584</v>
+      </c>
+      <c r="C175" s="0" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175">
-        <v>168</v>
-      </c>
-      <c r="B175">
-        <v>584</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="D175" s="0" t="s">
         <v>655</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="F175" t="s">
+    </row>
+    <row r="176">
+      <c r="A176" s="0">
+        <v>169</v>
+      </c>
+      <c r="B176" s="0">
+        <v>585</v>
+      </c>
+      <c r="C176" s="0" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176">
-        <v>169</v>
-      </c>
-      <c r="B176">
-        <v>585</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="D176" s="0" t="s">
         <v>659</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" s="0" t="s">
         <v>660</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" s="0" t="s">
         <v>661</v>
       </c>
-      <c r="F176" t="s">
+    </row>
+    <row r="177">
+      <c r="A177" s="0">
+        <v>170</v>
+      </c>
+      <c r="B177" s="0">
+        <v>586</v>
+      </c>
+      <c r="C177" s="0" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177">
-        <v>170</v>
-      </c>
-      <c r="B177">
-        <v>586</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="D177" s="0" t="s">
         <v>663</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" s="0" t="s">
         <v>664</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" s="0" t="s">
         <v>665</v>
       </c>
-      <c r="F177" t="s">
+    </row>
+    <row r="178">
+      <c r="A178" s="0">
+        <v>171</v>
+      </c>
+      <c r="B178" s="0">
+        <v>591</v>
+      </c>
+      <c r="C178" s="0" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178">
-        <v>171</v>
-      </c>
-      <c r="B178">
-        <v>591</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="D178" s="0" t="s">
         <v>667</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" s="0" t="s">
         <v>668</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="F178" t="s">
+    </row>
+    <row r="179">
+      <c r="A179" s="0">
+        <v>172</v>
+      </c>
+      <c r="B179" s="0">
+        <v>598</v>
+      </c>
+      <c r="C179" s="0" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179">
-        <v>172</v>
-      </c>
-      <c r="B179">
-        <v>598</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="D179" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" s="0" t="s">
         <v>672</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="F179" t="s">
+    </row>
+    <row r="180">
+      <c r="A180" s="0">
+        <v>173</v>
+      </c>
+      <c r="B180" s="0">
+        <v>600</v>
+      </c>
+      <c r="C180" s="0" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180">
-        <v>173</v>
-      </c>
-      <c r="B180">
-        <v>600</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="D180" s="0" t="s">
         <v>675</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" s="0" t="s">
         <v>677</v>
       </c>
-      <c r="F180" t="s">
+    </row>
+    <row r="181">
+      <c r="A181" s="0">
+        <v>174</v>
+      </c>
+      <c r="B181" s="0">
+        <v>604</v>
+      </c>
+      <c r="C181" s="0" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181">
-        <v>174</v>
-      </c>
-      <c r="B181">
-        <v>604</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="D181" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" s="0" t="s">
         <v>680</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="F181" t="s">
+    </row>
+    <row r="182">
+      <c r="A182" s="0">
+        <v>175</v>
+      </c>
+      <c r="B182" s="0">
+        <v>608</v>
+      </c>
+      <c r="C182" s="0" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182">
-        <v>175</v>
-      </c>
-      <c r="B182">
-        <v>608</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="D182" s="0" t="s">
         <v>683</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" s="0" t="s">
         <v>684</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" s="0" t="s">
         <v>685</v>
       </c>
-      <c r="F182" t="s">
+    </row>
+    <row r="183">
+      <c r="A183" s="0">
+        <v>176</v>
+      </c>
+      <c r="B183" s="0">
+        <v>612</v>
+      </c>
+      <c r="C183" s="0" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183">
-        <v>176</v>
-      </c>
-      <c r="B183">
-        <v>612</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="D183"/>
+      <c r="E183" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="D183"/>
-      <c r="E183" t="s">
+      <c r="F183" s="0" t="s">
         <v>688</v>
       </c>
-      <c r="F183" t="s">
+    </row>
+    <row r="184">
+      <c r="A184" s="0">
+        <v>177</v>
+      </c>
+      <c r="B184" s="0">
+        <v>616</v>
+      </c>
+      <c r="C184" s="0" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184">
-        <v>177</v>
-      </c>
-      <c r="B184">
-        <v>616</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="D184" s="0" t="s">
         <v>690</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" s="0" t="s">
         <v>692</v>
       </c>
-      <c r="F184" t="s">
+    </row>
+    <row r="185">
+      <c r="A185" s="0">
+        <v>178</v>
+      </c>
+      <c r="B185" s="0">
+        <v>620</v>
+      </c>
+      <c r="C185" s="0" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185">
-        <v>178</v>
-      </c>
-      <c r="B185">
-        <v>620</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="D185" s="0" t="s">
         <v>694</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" s="0" t="s">
         <v>695</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" s="0" t="s">
         <v>696</v>
       </c>
-      <c r="F185" t="s">
+    </row>
+    <row r="186">
+      <c r="A186" s="0">
+        <v>179</v>
+      </c>
+      <c r="B186" s="0">
+        <v>624</v>
+      </c>
+      <c r="C186" s="0" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186">
-        <v>179</v>
-      </c>
-      <c r="B186">
-        <v>624</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="D186" s="0" t="s">
         <v>698</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" s="0" t="s">
         <v>699</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="F186" t="s">
+    </row>
+    <row r="187">
+      <c r="A187" s="0">
+        <v>180</v>
+      </c>
+      <c r="B187" s="0">
+        <v>626</v>
+      </c>
+      <c r="C187" s="0" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187">
-        <v>180</v>
-      </c>
-      <c r="B187">
-        <v>626</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="D187" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" s="0" t="s">
         <v>703</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" s="0" t="s">
         <v>704</v>
       </c>
-      <c r="F187" t="s">
+    </row>
+    <row r="188">
+      <c r="A188" s="0">
+        <v>181</v>
+      </c>
+      <c r="B188" s="0">
+        <v>630</v>
+      </c>
+      <c r="C188" s="0" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188">
-        <v>181</v>
-      </c>
-      <c r="B188">
-        <v>630</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="D188"/>
+      <c r="E188" s="0" t="s">
         <v>706</v>
       </c>
-      <c r="D188"/>
-      <c r="E188" t="s">
+      <c r="F188" s="0" t="s">
         <v>707</v>
       </c>
-      <c r="F188" t="s">
+    </row>
+    <row r="189">
+      <c r="A189" s="0">
+        <v>182</v>
+      </c>
+      <c r="B189" s="0">
+        <v>634</v>
+      </c>
+      <c r="C189" s="0" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189">
-        <v>182</v>
-      </c>
-      <c r="B189">
-        <v>634</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="D189" s="0" t="s">
         <v>709</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" s="0" t="s">
         <v>710</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" s="0" t="s">
         <v>711</v>
       </c>
-      <c r="F189" t="s">
+    </row>
+    <row r="190">
+      <c r="A190" s="0">
+        <v>183</v>
+      </c>
+      <c r="B190" s="0">
+        <v>638</v>
+      </c>
+      <c r="C190" s="0" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190">
-        <v>183</v>
-      </c>
-      <c r="B190">
-        <v>638</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="D190"/>
+      <c r="E190" s="0" t="s">
         <v>713</v>
       </c>
-      <c r="D190"/>
-      <c r="E190" t="s">
+      <c r="F190" s="0" t="s">
         <v>714</v>
       </c>
-      <c r="F190" t="s">
+    </row>
+    <row r="191">
+      <c r="A191" s="0">
+        <v>184</v>
+      </c>
+      <c r="B191" s="0">
+        <v>642</v>
+      </c>
+      <c r="C191" s="0" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191">
-        <v>184</v>
-      </c>
-      <c r="B191">
-        <v>642</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="D191"/>
+      <c r="E191" s="0" t="s">
         <v>716</v>
       </c>
-      <c r="D191"/>
-      <c r="E191" t="s">
+      <c r="F191" s="0" t="s">
         <v>717</v>
       </c>
-      <c r="F191" t="s">
+    </row>
+    <row r="192">
+      <c r="A192" s="0">
+        <v>185</v>
+      </c>
+      <c r="B192" s="0">
+        <v>643</v>
+      </c>
+      <c r="C192" s="0" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192">
-        <v>185</v>
-      </c>
-      <c r="B192">
-        <v>643</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="D192" s="0" t="s">
         <v>719</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" s="0" t="s">
         <v>720</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="F192" t="s">
+    </row>
+    <row r="193">
+      <c r="A193" s="0">
+        <v>186</v>
+      </c>
+      <c r="B193" s="0">
+        <v>646</v>
+      </c>
+      <c r="C193" s="0" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193">
-        <v>186</v>
-      </c>
-      <c r="B193">
-        <v>646</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="D193" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" s="0" t="s">
         <v>725</v>
       </c>
-      <c r="F193" t="s">
+    </row>
+    <row r="194">
+      <c r="A194" s="0">
+        <v>187</v>
+      </c>
+      <c r="B194" s="0">
+        <v>652</v>
+      </c>
+      <c r="C194" s="0" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194">
-        <v>187</v>
-      </c>
-      <c r="B194">
-        <v>652</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="D194"/>
+      <c r="E194" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="D194"/>
-      <c r="E194" t="s">
+      <c r="F194" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="F194" t="s">
+    </row>
+    <row r="195">
+      <c r="A195" s="0">
+        <v>188</v>
+      </c>
+      <c r="B195" s="0">
+        <v>654</v>
+      </c>
+      <c r="C195" s="0" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195">
-        <v>188</v>
-      </c>
-      <c r="B195">
-        <v>654</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="D195"/>
+      <c r="E195" s="0" t="s">
         <v>730</v>
       </c>
-      <c r="D195"/>
-      <c r="E195" t="s">
+      <c r="F195" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="F195" t="s">
+    </row>
+    <row r="196">
+      <c r="A196" s="0">
+        <v>189</v>
+      </c>
+      <c r="B196" s="0">
+        <v>659</v>
+      </c>
+      <c r="C196" s="0" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196">
-        <v>189</v>
-      </c>
-      <c r="B196">
-        <v>659</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="D196"/>
+      <c r="E196" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="D196"/>
-      <c r="E196" t="s">
+      <c r="F196" s="0" t="s">
         <v>734</v>
       </c>
-      <c r="F196" t="s">
+    </row>
+    <row r="197">
+      <c r="A197" s="0">
+        <v>190</v>
+      </c>
+      <c r="B197" s="0">
+        <v>660</v>
+      </c>
+      <c r="C197" s="0" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197">
-        <v>190</v>
-      </c>
-      <c r="B197">
-        <v>660</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="D197"/>
+      <c r="E197" s="0" t="s">
         <v>736</v>
       </c>
-      <c r="D197"/>
-      <c r="E197" t="s">
+      <c r="F197" s="0" t="s">
         <v>737</v>
       </c>
-      <c r="F197" t="s">
+    </row>
+    <row r="198">
+      <c r="A198" s="0">
+        <v>191</v>
+      </c>
+      <c r="B198" s="0">
+        <v>662</v>
+      </c>
+      <c r="C198" s="0" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198">
-        <v>191</v>
-      </c>
-      <c r="B198">
-        <v>662</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="D198"/>
+      <c r="E198" s="0" t="s">
         <v>739</v>
       </c>
-      <c r="D198"/>
-      <c r="E198" t="s">
+      <c r="F198" s="0" t="s">
         <v>740</v>
       </c>
-      <c r="F198" t="s">
+    </row>
+    <row r="199">
+      <c r="A199" s="0">
+        <v>192</v>
+      </c>
+      <c r="B199" s="0">
+        <v>663</v>
+      </c>
+      <c r="C199" s="0" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199">
-        <v>192</v>
-      </c>
-      <c r="B199">
-        <v>663</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="D199"/>
+      <c r="E199" s="0" t="s">
         <v>742</v>
       </c>
-      <c r="D199"/>
-      <c r="E199" t="s">
+      <c r="F199" s="0" t="s">
         <v>743</v>
       </c>
-      <c r="F199" t="s">
+    </row>
+    <row r="200">
+      <c r="A200" s="0">
+        <v>193</v>
+      </c>
+      <c r="B200" s="0">
+        <v>666</v>
+      </c>
+      <c r="C200" s="0" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200">
-        <v>193</v>
-      </c>
-      <c r="B200">
-        <v>666</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="D200"/>
+      <c r="E200" s="0" t="s">
         <v>745</v>
       </c>
-      <c r="D200"/>
-      <c r="E200" t="s">
+      <c r="F200" s="0" t="s">
         <v>746</v>
       </c>
-      <c r="F200" t="s">
+    </row>
+    <row r="201">
+      <c r="A201" s="0">
+        <v>194</v>
+      </c>
+      <c r="B201" s="0">
+        <v>670</v>
+      </c>
+      <c r="C201" s="0" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201">
-        <v>194</v>
-      </c>
-      <c r="B201">
-        <v>670</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="D201"/>
+      <c r="E201" s="0" t="s">
         <v>748</v>
       </c>
-      <c r="D201"/>
-      <c r="E201" t="s">
+      <c r="F201" s="0" t="s">
         <v>749</v>
       </c>
-      <c r="F201" t="s">
+    </row>
+    <row r="202">
+      <c r="A202" s="0">
+        <v>195</v>
+      </c>
+      <c r="B202" s="0">
+        <v>674</v>
+      </c>
+      <c r="C202" s="0" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202">
-        <v>195</v>
-      </c>
-      <c r="B202">
-        <v>674</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="D202" s="0" t="s">
         <v>751</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" s="0" t="s">
         <v>752</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" s="0" t="s">
         <v>753</v>
       </c>
-      <c r="F202" t="s">
+    </row>
+    <row r="203">
+      <c r="A203" s="0">
+        <v>196</v>
+      </c>
+      <c r="B203" s="0">
+        <v>678</v>
+      </c>
+      <c r="C203" s="0" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203">
-        <v>196</v>
-      </c>
-      <c r="B203">
-        <v>678</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="D203" s="0" t="s">
         <v>755</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" s="0" t="s">
         <v>757</v>
       </c>
-      <c r="F203" t="s">
+    </row>
+    <row r="204">
+      <c r="A204" s="0">
+        <v>197</v>
+      </c>
+      <c r="B204" s="0">
+        <v>682</v>
+      </c>
+      <c r="C204" s="0" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204">
-        <v>197</v>
-      </c>
-      <c r="B204">
-        <v>682</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="D204" s="0" t="s">
         <v>759</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" s="0" t="s">
         <v>760</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" s="0" t="s">
         <v>761</v>
       </c>
-      <c r="F204" t="s">
+    </row>
+    <row r="205">
+      <c r="A205" s="0">
+        <v>198</v>
+      </c>
+      <c r="B205" s="0">
+        <v>686</v>
+      </c>
+      <c r="C205" s="0" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205">
-        <v>198</v>
-      </c>
-      <c r="B205">
-        <v>686</v>
-      </c>
-      <c r="C205" t="s">
+      <c r="D205" s="0" t="s">
         <v>763</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" s="0" t="s">
         <v>764</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" s="0" t="s">
         <v>765</v>
       </c>
-      <c r="F205" t="s">
+    </row>
+    <row r="206">
+      <c r="A206" s="0">
+        <v>199</v>
+      </c>
+      <c r="B206" s="0">
+        <v>688</v>
+      </c>
+      <c r="C206" s="0" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206">
-        <v>199</v>
-      </c>
-      <c r="B206">
-        <v>688</v>
-      </c>
-      <c r="C206" t="s">
+      <c r="D206" s="0" t="s">
         <v>767</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" s="0" t="s">
         <v>768</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" s="0" t="s">
         <v>769</v>
       </c>
-      <c r="F206" t="s">
+    </row>
+    <row r="207">
+      <c r="A207" s="0">
+        <v>200</v>
+      </c>
+      <c r="B207" s="0">
+        <v>690</v>
+      </c>
+      <c r="C207" s="0" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207">
-        <v>200</v>
-      </c>
-      <c r="B207">
-        <v>690</v>
-      </c>
-      <c r="C207" t="s">
+      <c r="D207" s="0" t="s">
         <v>771</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" s="0" t="s">
         <v>772</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" s="0" t="s">
         <v>773</v>
       </c>
-      <c r="F207" t="s">
+    </row>
+    <row r="208">
+      <c r="A208" s="0">
+        <v>201</v>
+      </c>
+      <c r="B208" s="0">
+        <v>694</v>
+      </c>
+      <c r="C208" s="0" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208">
-        <v>201</v>
-      </c>
-      <c r="B208">
-        <v>694</v>
-      </c>
-      <c r="C208" t="s">
+      <c r="D208" s="0" t="s">
         <v>775</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" s="0" t="s">
         <v>777</v>
       </c>
-      <c r="F208" t="s">
+    </row>
+    <row r="209">
+      <c r="A209" s="0">
+        <v>202</v>
+      </c>
+      <c r="B209" s="0">
+        <v>702</v>
+      </c>
+      <c r="C209" s="0" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209">
-        <v>202</v>
-      </c>
-      <c r="B209">
-        <v>702</v>
-      </c>
-      <c r="C209" t="s">
+      <c r="D209" s="0" t="s">
         <v>779</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" s="0" t="s">
         <v>780</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" s="0" t="s">
         <v>781</v>
       </c>
-      <c r="F209" t="s">
+    </row>
+    <row r="210">
+      <c r="A210" s="0">
+        <v>203</v>
+      </c>
+      <c r="B210" s="0">
+        <v>703</v>
+      </c>
+      <c r="C210" s="0" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210">
-        <v>203</v>
-      </c>
-      <c r="B210">
-        <v>703</v>
-      </c>
-      <c r="C210" t="s">
+      <c r="D210" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" s="0" t="s">
         <v>784</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" s="0" t="s">
         <v>785</v>
       </c>
-      <c r="F210" t="s">
+    </row>
+    <row r="211">
+      <c r="A211" s="0">
+        <v>204</v>
+      </c>
+      <c r="B211" s="0">
+        <v>704</v>
+      </c>
+      <c r="C211" s="0" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211">
-        <v>204</v>
-      </c>
-      <c r="B211">
-        <v>704</v>
-      </c>
-      <c r="C211" t="s">
+      <c r="D211" s="0" t="s">
         <v>787</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" s="0" t="s">
         <v>788</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" s="0" t="s">
         <v>789</v>
       </c>
-      <c r="F211" t="s">
+    </row>
+    <row r="212">
+      <c r="A212" s="0">
+        <v>205</v>
+      </c>
+      <c r="B212" s="0">
+        <v>705</v>
+      </c>
+      <c r="C212" s="0" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212">
-        <v>205</v>
-      </c>
-      <c r="B212">
-        <v>705</v>
-      </c>
-      <c r="C212" t="s">
+      <c r="D212" s="0" t="s">
         <v>791</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" s="0" t="s">
         <v>792</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" s="0" t="s">
         <v>793</v>
       </c>
-      <c r="F212" t="s">
+    </row>
+    <row r="213">
+      <c r="A213" s="0">
+        <v>206</v>
+      </c>
+      <c r="B213" s="0">
+        <v>706</v>
+      </c>
+      <c r="C213" s="0" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213">
-        <v>206</v>
-      </c>
-      <c r="B213">
-        <v>706</v>
-      </c>
-      <c r="C213" t="s">
+      <c r="D213" s="0" t="s">
         <v>795</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" s="0" t="s">
         <v>796</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" s="0" t="s">
         <v>797</v>
       </c>
-      <c r="F213" t="s">
+    </row>
+    <row r="214">
+      <c r="A214" s="0">
+        <v>207</v>
+      </c>
+      <c r="B214" s="0">
+        <v>710</v>
+      </c>
+      <c r="C214" s="0" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214">
-        <v>207</v>
-      </c>
-      <c r="B214">
-        <v>710</v>
-      </c>
-      <c r="C214" t="s">
+      <c r="D214" s="0" t="s">
         <v>799</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" s="0" t="s">
         <v>800</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" s="0" t="s">
         <v>801</v>
       </c>
-      <c r="F214" t="s">
+    </row>
+    <row r="215">
+      <c r="A215" s="0">
+        <v>208</v>
+      </c>
+      <c r="B215" s="0">
+        <v>716</v>
+      </c>
+      <c r="C215" s="0" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215">
-        <v>208</v>
-      </c>
-      <c r="B215">
-        <v>716</v>
-      </c>
-      <c r="C215" t="s">
+      <c r="D215" s="0" t="s">
         <v>803</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" s="0" t="s">
         <v>804</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" s="0" t="s">
         <v>805</v>
       </c>
-      <c r="F215" t="s">
+    </row>
+    <row r="216">
+      <c r="A216" s="0">
+        <v>209</v>
+      </c>
+      <c r="B216" s="0">
+        <v>724</v>
+      </c>
+      <c r="C216" s="0" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216">
-        <v>209</v>
-      </c>
-      <c r="B216">
-        <v>724</v>
-      </c>
-      <c r="C216" t="s">
+      <c r="D216" s="0" t="s">
         <v>807</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" s="0" t="s">
         <v>808</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="F216" t="s">
+    </row>
+    <row r="217">
+      <c r="A217" s="0">
+        <v>210</v>
+      </c>
+      <c r="B217" s="0">
+        <v>728</v>
+      </c>
+      <c r="C217" s="0" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217">
-        <v>210</v>
-      </c>
-      <c r="B217">
+      <c r="D217" s="0" t="s">
+        <v>811</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>812</v>
+      </c>
+      <c r="F217" s="0" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0">
+        <v>211</v>
+      </c>
+      <c r="B218" s="0">
+        <v>729</v>
+      </c>
+      <c r="C218" s="0" t="s">
+        <v>814</v>
+      </c>
+      <c r="D218" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="E218" s="0" t="s">
+        <v>816</v>
+      </c>
+      <c r="F218" s="0" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0">
+        <v>212</v>
+      </c>
+      <c r="B219" s="0">
         <v>732</v>
       </c>
-      <c r="C217" t="s">
-        <v>811</v>
-      </c>
-      <c r="D217"/>
-      <c r="E217" t="s">
-        <v>812</v>
-      </c>
-      <c r="F217" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218">
-        <v>211</v>
-      </c>
-      <c r="B218">
-        <v>729</v>
-      </c>
-      <c r="C218" t="s">
-        <v>814</v>
-      </c>
-      <c r="D218" t="s">
-        <v>815</v>
-      </c>
-      <c r="E218" t="s">
-        <v>816</v>
-      </c>
-      <c r="F218" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219">
-        <v>212</v>
-      </c>
-      <c r="B219">
+      <c r="C219" s="0" t="s">
+        <v>818</v>
+      </c>
+      <c r="D219"/>
+      <c r="E219" s="0" t="s">
+        <v>819</v>
+      </c>
+      <c r="F219" s="0" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0">
+        <v>213</v>
+      </c>
+      <c r="B220" s="0">
         <v>740</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C220" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="D220" s="0" t="s">
+        <v>822</v>
+      </c>
+      <c r="E220" s="0" t="s">
+        <v>823</v>
+      </c>
+      <c r="F220" s="0" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0">
+        <v>214</v>
+      </c>
+      <c r="B221" s="0">
+        <v>744</v>
+      </c>
+      <c r="C221" s="0" t="s">
+        <v>825</v>
+      </c>
+      <c r="D221"/>
+      <c r="E221" s="0" t="s">
+        <v>826</v>
+      </c>
+      <c r="F221" s="0" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0">
+        <v>215</v>
+      </c>
+      <c r="B222" s="0">
+        <v>748</v>
+      </c>
+      <c r="C222" s="0" t="s">
+        <v>828</v>
+      </c>
+      <c r="D222" s="0" t="s">
+        <v>829</v>
+      </c>
+      <c r="E222" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="F222" s="0" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0">
+        <v>216</v>
+      </c>
+      <c r="B223" s="0">
+        <v>752</v>
+      </c>
+      <c r="C223" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="D223" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="E223" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="F223" s="0" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0">
+        <v>217</v>
+      </c>
+      <c r="B224" s="0">
+        <v>756</v>
+      </c>
+      <c r="C224" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D224" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="E224" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="F224" s="0" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0">
+        <v>218</v>
+      </c>
+      <c r="B225" s="0">
+        <v>760</v>
+      </c>
+      <c r="C225" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D225"/>
+      <c r="E225" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="F225" s="0" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0">
+        <v>219</v>
+      </c>
+      <c r="B226" s="0">
+        <v>762</v>
+      </c>
+      <c r="C226" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D226" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="E226" s="0" t="s">
+        <v>845</v>
+      </c>
+      <c r="F226" s="0" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0">
+        <v>220</v>
+      </c>
+      <c r="B227" s="0">
+        <v>764</v>
+      </c>
+      <c r="C227" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D227" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="E227" s="0" t="s">
+        <v>849</v>
+      </c>
+      <c r="F227" s="0" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0">
+        <v>221</v>
+      </c>
+      <c r="B228" s="0">
+        <v>768</v>
+      </c>
+      <c r="C228" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="D228" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="E228" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="F228" s="0" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0">
+        <v>222</v>
+      </c>
+      <c r="B229" s="0">
+        <v>772</v>
+      </c>
+      <c r="C229" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="D229"/>
+      <c r="E229" s="0" t="s">
+        <v>856</v>
+      </c>
+      <c r="F229" s="0" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0">
+        <v>223</v>
+      </c>
+      <c r="B230" s="0">
+        <v>776</v>
+      </c>
+      <c r="C230" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="D230" s="0" t="s">
+        <v>859</v>
+      </c>
+      <c r="E230" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="F230" s="0" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0">
+        <v>224</v>
+      </c>
+      <c r="B231" s="0">
+        <v>780</v>
+      </c>
+      <c r="C231" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="D231" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="E231" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="F231" s="0" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0">
+        <v>225</v>
+      </c>
+      <c r="B232" s="0">
+        <v>784</v>
+      </c>
+      <c r="C232" s="0" t="s">
+        <v>866</v>
+      </c>
+      <c r="D232"/>
+      <c r="E232" s="0" t="s">
+        <v>867</v>
+      </c>
+      <c r="F232" s="0" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0">
+        <v>226</v>
+      </c>
+      <c r="B233" s="0">
+        <v>788</v>
+      </c>
+      <c r="C233" s="0" t="s">
+        <v>869</v>
+      </c>
+      <c r="D233" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="E233" s="0" t="s">
+        <v>871</v>
+      </c>
+      <c r="F233" s="0" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0">
+        <v>227</v>
+      </c>
+      <c r="B234" s="0">
+        <v>792</v>
+      </c>
+      <c r="C234" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="D234" s="0" t="s">
+        <v>874</v>
+      </c>
+      <c r="E234" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="F234" s="0" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0">
+        <v>228</v>
+      </c>
+      <c r="B235" s="0">
+        <v>795</v>
+      </c>
+      <c r="C235" s="0" t="s">
+        <v>877</v>
+      </c>
+      <c r="D235" s="0" t="s">
+        <v>878</v>
+      </c>
+      <c r="E235" s="0" t="s">
+        <v>879</v>
+      </c>
+      <c r="F235" s="0" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0">
+        <v>229</v>
+      </c>
+      <c r="B236" s="0">
+        <v>796</v>
+      </c>
+      <c r="C236" s="0" t="s">
+        <v>881</v>
+      </c>
+      <c r="D236"/>
+      <c r="E236" s="0" t="s">
+        <v>882</v>
+      </c>
+      <c r="F236" s="0" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0">
+        <v>230</v>
+      </c>
+      <c r="B237" s="0">
+        <v>798</v>
+      </c>
+      <c r="C237" s="0" t="s">
+        <v>884</v>
+      </c>
+      <c r="D237"/>
+      <c r="E237" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="F237" s="0" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0">
+        <v>231</v>
+      </c>
+      <c r="B238" s="0">
+        <v>800</v>
+      </c>
+      <c r="C238" s="0" t="s">
+        <v>887</v>
+      </c>
+      <c r="D238" s="0" t="s">
+        <v>888</v>
+      </c>
+      <c r="E238" s="0" t="s">
+        <v>889</v>
+      </c>
+      <c r="F238" s="0" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0">
+        <v>232</v>
+      </c>
+      <c r="B239" s="0">
+        <v>804</v>
+      </c>
+      <c r="C239" s="0" t="s">
+        <v>891</v>
+      </c>
+      <c r="D239"/>
+      <c r="E239" s="0" t="s">
+        <v>892</v>
+      </c>
+      <c r="F239" s="0" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0">
+        <v>233</v>
+      </c>
+      <c r="B240" s="0">
+        <v>807</v>
+      </c>
+      <c r="C240" s="0" t="s">
+        <v>894</v>
+      </c>
+      <c r="D240" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="E240" s="0" t="s">
+        <v>896</v>
+      </c>
+      <c r="F240" s="0" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0">
+        <v>234</v>
+      </c>
+      <c r="B241" s="0">
         <v>818</v>
       </c>
-      <c r="D219" t="s">
-        <v>819</v>
-      </c>
-      <c r="E219" t="s">
-        <v>820</v>
-      </c>
-      <c r="F219" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220">
-        <v>213</v>
-      </c>
-      <c r="B220">
-        <v>744</v>
-      </c>
-      <c r="C220" t="s">
-        <v>822</v>
-      </c>
-      <c r="D220"/>
-      <c r="E220" t="s">
-        <v>823</v>
-      </c>
-      <c r="F220" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
-        <v>214</v>
-      </c>
-      <c r="B221">
-        <v>748</v>
-      </c>
-      <c r="C221" t="s">
-        <v>825</v>
-      </c>
-      <c r="D221" t="s">
+      <c r="C241" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="D241" s="0" t="s">
+        <v>899</v>
+      </c>
+      <c r="E241" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="F241" s="0" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0">
+        <v>235</v>
+      </c>
+      <c r="B242" s="0">
         <v>826</v>
       </c>
-      <c r="E221" t="s">
-        <v>827</v>
-      </c>
-      <c r="F221" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222">
-        <v>215</v>
-      </c>
-      <c r="B222">
-        <v>752</v>
-      </c>
-      <c r="C222" t="s">
-        <v>829</v>
-      </c>
-      <c r="D222" t="s">
-        <v>830</v>
-      </c>
-      <c r="E222" t="s">
+      <c r="C242" s="0" t="s">
+        <v>902</v>
+      </c>
+      <c r="D242"/>
+      <c r="E242" s="0" t="s">
+        <v>903</v>
+      </c>
+      <c r="F242" s="0" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0">
+        <v>236</v>
+      </c>
+      <c r="B243" s="0">
         <v>831</v>
       </c>
-      <c r="F222" t="s">
+      <c r="C243" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="D243"/>
+      <c r="E243" s="0" t="s">
+        <v>906</v>
+      </c>
+      <c r="F243" s="0" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0">
+        <v>237</v>
+      </c>
+      <c r="B244" s="0">
         <v>832</v>
       </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223">
-        <v>216</v>
-      </c>
-      <c r="B223">
-        <v>756</v>
-      </c>
-      <c r="C223" t="s">
+      <c r="C244" s="0" t="s">
+        <v>908</v>
+      </c>
+      <c r="D244"/>
+      <c r="E244" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="F244" s="0" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0">
+        <v>238</v>
+      </c>
+      <c r="B245" s="0">
         <v>833</v>
       </c>
-      <c r="D223" t="s">
+      <c r="C245" s="0" t="s">
+        <v>911</v>
+      </c>
+      <c r="D245"/>
+      <c r="E245" s="0" t="s">
+        <v>912</v>
+      </c>
+      <c r="F245" s="0" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0">
+        <v>239</v>
+      </c>
+      <c r="B246" s="0">
         <v>834</v>
       </c>
-      <c r="E223" t="s">
-        <v>835</v>
-      </c>
-      <c r="F223" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224">
-        <v>217</v>
-      </c>
-      <c r="B224">
-        <v>760</v>
-      </c>
-      <c r="C224" t="s">
-        <v>837</v>
-      </c>
-      <c r="D224"/>
-      <c r="E224" t="s">
-        <v>838</v>
-      </c>
-      <c r="F224" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225">
-        <v>218</v>
-      </c>
-      <c r="B225">
-        <v>762</v>
-      </c>
-      <c r="C225" t="s">
+      <c r="C246" s="0" t="s">
+        <v>914</v>
+      </c>
+      <c r="D246" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="E246" s="0" t="s">
+        <v>916</v>
+      </c>
+      <c r="F246" s="0" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0">
+        <v>240</v>
+      </c>
+      <c r="B247" s="0">
         <v>840</v>
       </c>
-      <c r="D225" t="s">
-        <v>841</v>
-      </c>
-      <c r="E225" t="s">
-        <v>842</v>
-      </c>
-      <c r="F225" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226">
-        <v>219</v>
-      </c>
-      <c r="B226">
-        <v>764</v>
-      </c>
-      <c r="C226" t="s">
-        <v>844</v>
-      </c>
-      <c r="D226" t="s">
-        <v>845</v>
-      </c>
-      <c r="E226" t="s">
-        <v>846</v>
-      </c>
-      <c r="F226" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227">
-        <v>220</v>
-      </c>
-      <c r="B227">
-        <v>768</v>
-      </c>
-      <c r="C227" t="s">
-        <v>848</v>
-      </c>
-      <c r="D227" t="s">
-        <v>849</v>
-      </c>
-      <c r="E227" t="s">
+      <c r="C247" s="0" t="s">
+        <v>918</v>
+      </c>
+      <c r="D247" s="0" t="s">
+        <v>919</v>
+      </c>
+      <c r="E247" s="0" t="s">
+        <v>920</v>
+      </c>
+      <c r="F247" s="0" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0">
+        <v>241</v>
+      </c>
+      <c r="B248" s="0">
         <v>850</v>
       </c>
-      <c r="F227" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228">
-        <v>221</v>
-      </c>
-      <c r="B228">
-        <v>772</v>
-      </c>
-      <c r="C228" t="s">
-        <v>852</v>
-      </c>
-      <c r="D228"/>
-      <c r="E228" t="s">
-        <v>853</v>
-      </c>
-      <c r="F228" t="s">
+      <c r="C248" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="D248" s="0" t="s">
+        <v>923</v>
+      </c>
+      <c r="E248" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="F248" s="0" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0">
+        <v>242</v>
+      </c>
+      <c r="B249" s="0">
         <v>854</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229">
-        <v>222</v>
-      </c>
-      <c r="B229">
-        <v>776</v>
-      </c>
-      <c r="C229" t="s">
-        <v>855</v>
-      </c>
-      <c r="D229" t="s">
-        <v>856</v>
-      </c>
-      <c r="E229" t="s">
-        <v>857</v>
-      </c>
-      <c r="F229" t="s">
+      <c r="C249" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="D249"/>
+      <c r="E249" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="F249" s="0" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0">
+        <v>243</v>
+      </c>
+      <c r="B250" s="0">
         <v>858</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230">
-        <v>223</v>
-      </c>
-      <c r="B230">
-        <v>780</v>
-      </c>
-      <c r="C230" t="s">
-        <v>859</v>
-      </c>
-      <c r="D230" t="s">
+      <c r="C250" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="D250" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="E250" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="F250" s="0" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0">
+        <v>244</v>
+      </c>
+      <c r="B251" s="0">
         <v>860</v>
       </c>
-      <c r="E230" t="s">
-        <v>861</v>
-      </c>
-      <c r="F230" t="s">
+      <c r="C251" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="D251" s="0" t="s">
+        <v>934</v>
+      </c>
+      <c r="E251" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="F251" s="0" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0">
+        <v>245</v>
+      </c>
+      <c r="B252" s="0">
         <v>862</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231">
-        <v>224</v>
-      </c>
-      <c r="B231">
-        <v>784</v>
-      </c>
-      <c r="C231" t="s">
-        <v>863</v>
-      </c>
-      <c r="D231"/>
-      <c r="E231" t="s">
-        <v>864</v>
-      </c>
-      <c r="F231" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232">
-        <v>225</v>
-      </c>
-      <c r="B232">
-        <v>788</v>
-      </c>
-      <c r="C232" t="s">
-        <v>866</v>
-      </c>
-      <c r="D232" t="s">
-        <v>867</v>
-      </c>
-      <c r="E232" t="s">
-        <v>868</v>
-      </c>
-      <c r="F232" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233">
-        <v>226</v>
-      </c>
-      <c r="B233">
-        <v>792</v>
-      </c>
-      <c r="C233" t="s">
-        <v>870</v>
-      </c>
-      <c r="D233" t="s">
-        <v>871</v>
-      </c>
-      <c r="E233" t="s">
-        <v>872</v>
-      </c>
-      <c r="F233" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234">
-        <v>227</v>
-      </c>
-      <c r="B234">
-        <v>795</v>
-      </c>
-      <c r="C234" t="s">
-        <v>874</v>
-      </c>
-      <c r="D234" t="s">
-        <v>875</v>
-      </c>
-      <c r="E234" t="s">
+      <c r="C252" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="D252" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="E252" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="F252" s="0" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0">
+        <v>246</v>
+      </c>
+      <c r="B253" s="0">
         <v>876</v>
       </c>
-      <c r="F234" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235">
-        <v>228</v>
-      </c>
-      <c r="B235">
-        <v>796</v>
-      </c>
-      <c r="C235" t="s">
-        <v>878</v>
-      </c>
-      <c r="D235"/>
-      <c r="E235" t="s">
-        <v>879</v>
-      </c>
-      <c r="F235" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236">
-        <v>229</v>
-      </c>
-      <c r="B236">
-        <v>798</v>
-      </c>
-      <c r="C236" t="s">
-        <v>881</v>
-      </c>
-      <c r="D236"/>
-      <c r="E236" t="s">
+      <c r="C253" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="D253"/>
+      <c r="E253" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="F253" s="0" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0">
+        <v>247</v>
+      </c>
+      <c r="B254" s="0">
         <v>882</v>
       </c>
-      <c r="F236" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237">
-        <v>230</v>
-      </c>
-      <c r="B237">
-        <v>800</v>
-      </c>
-      <c r="C237" t="s">
-        <v>884</v>
-      </c>
-      <c r="D237" t="s">
-        <v>885</v>
-      </c>
-      <c r="E237" t="s">
-        <v>886</v>
-      </c>
-      <c r="F237" t="s">
+      <c r="C254" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="D254" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="E254" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="F254" s="0" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0">
+        <v>248</v>
+      </c>
+      <c r="B255" s="0">
         <v>887</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238">
-        <v>231</v>
-      </c>
-      <c r="B238">
-        <v>804</v>
-      </c>
-      <c r="C238" t="s">
-        <v>888</v>
-      </c>
-      <c r="D238"/>
-      <c r="E238" t="s">
-        <v>889</v>
-      </c>
-      <c r="F238" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239">
-        <v>232</v>
-      </c>
-      <c r="B239">
-        <v>807</v>
-      </c>
-      <c r="C239" t="s">
-        <v>891</v>
-      </c>
-      <c r="D239" t="s">
-        <v>892</v>
-      </c>
-      <c r="E239" t="s">
-        <v>893</v>
-      </c>
-      <c r="F239" t="s">
+      <c r="C255" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="D255" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="E255" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="F255" s="0" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0">
+        <v>249</v>
+      </c>
+      <c r="B256" s="0">
         <v>894</v>
       </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240">
-        <v>233</v>
-      </c>
-      <c r="B240">
-        <v>818</v>
-      </c>
-      <c r="C240" t="s">
+      <c r="C256" s="0" t="s">
+        <v>952</v>
+      </c>
+      <c r="D256" s="0" t="s">
+        <v>953</v>
+      </c>
+      <c r="E256" s="0" t="s">
+        <v>954</v>
+      </c>
+      <c r="F256" s="0" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0">
+        <v>250</v>
+      </c>
+      <c r="B257" s="0">
         <v>895</v>
       </c>
-      <c r="D240" t="s">
+      <c r="C257" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="D257" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="E257" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="F257" s="0" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0">
+        <v>251</v>
+      </c>
+      <c r="B258" s="0">
         <v>896</v>
       </c>
-      <c r="E240" t="s">
+      <c r="C258" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="D258" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="E258" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="F258" s="0" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0">
+        <v>252</v>
+      </c>
+      <c r="B259" s="0">
         <v>897</v>
       </c>
-      <c r="F240" t="s">
+      <c r="C259" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="D259" s="0" t="s">
+        <v>965</v>
+      </c>
+      <c r="E259" s="0" t="s">
+        <v>966</v>
+      </c>
+      <c r="F259" s="0" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0">
+        <v>253</v>
+      </c>
+      <c r="B260" s="0">
         <v>898</v>
       </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241">
-        <v>234</v>
-      </c>
-      <c r="B241">
-        <v>826</v>
-      </c>
-      <c r="C241" t="s">
-        <v>899</v>
-      </c>
-      <c r="D241" t="s">
-        <v>900</v>
-      </c>
-      <c r="E241" t="s">
-        <v>901</v>
-      </c>
-      <c r="F241" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242">
-        <v>235</v>
-      </c>
-      <c r="B242">
-        <v>831</v>
-      </c>
-      <c r="C242" t="s">
-        <v>903</v>
-      </c>
-      <c r="D242"/>
-      <c r="E242" t="s">
-        <v>904</v>
-      </c>
-      <c r="F242" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243">
-        <v>236</v>
-      </c>
-      <c r="B243">
-        <v>832</v>
-      </c>
-      <c r="C243" t="s">
-        <v>906</v>
-      </c>
-      <c r="D243"/>
-      <c r="E243" t="s">
-        <v>907</v>
-      </c>
-      <c r="F243" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244">
-        <v>237</v>
-      </c>
-      <c r="B244">
-        <v>833</v>
-      </c>
-      <c r="C244" t="s">
-        <v>909</v>
-      </c>
-      <c r="D244"/>
-      <c r="E244" t="s">
-        <v>910</v>
-      </c>
-      <c r="F244" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245">
-        <v>238</v>
-      </c>
-      <c r="B245">
-        <v>834</v>
-      </c>
-      <c r="C245" t="s">
-        <v>912</v>
-      </c>
-      <c r="D245" t="s">
-        <v>913</v>
-      </c>
-      <c r="E245" t="s">
-        <v>914</v>
-      </c>
-      <c r="F245" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246">
-        <v>239</v>
-      </c>
-      <c r="B246">
-        <v>840</v>
-      </c>
-      <c r="C246" t="s">
-        <v>916</v>
-      </c>
-      <c r="D246" t="s">
-        <v>917</v>
-      </c>
-      <c r="E246" t="s">
-        <v>918</v>
-      </c>
-      <c r="F246" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247">
-        <v>240</v>
-      </c>
-      <c r="B247">
-        <v>850</v>
-      </c>
-      <c r="C247" t="s">
-        <v>920</v>
-      </c>
-      <c r="D247" t="s">
-        <v>921</v>
-      </c>
-      <c r="E247" t="s">
-        <v>922</v>
-      </c>
-      <c r="F247" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248">
-        <v>241</v>
-      </c>
-      <c r="B248">
-        <v>854</v>
-      </c>
-      <c r="C248" t="s">
-        <v>924</v>
-      </c>
-      <c r="D248"/>
-      <c r="E248" t="s">
-        <v>925</v>
-      </c>
-      <c r="F248" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249">
-        <v>242</v>
-      </c>
-      <c r="B249">
-        <v>858</v>
-      </c>
-      <c r="C249" t="s">
-        <v>927</v>
-      </c>
-      <c r="D249" t="s">
-        <v>928</v>
-      </c>
-      <c r="E249" t="s">
-        <v>929</v>
-      </c>
-      <c r="F249" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250">
-        <v>243</v>
-      </c>
-      <c r="B250">
-        <v>860</v>
-      </c>
-      <c r="C250" t="s">
-        <v>931</v>
-      </c>
-      <c r="D250" t="s">
-        <v>932</v>
-      </c>
-      <c r="E250" t="s">
-        <v>933</v>
-      </c>
-      <c r="F250" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251">
-        <v>244</v>
-      </c>
-      <c r="B251">
-        <v>862</v>
-      </c>
-      <c r="C251" t="s">
-        <v>935</v>
-      </c>
-      <c r="D251" t="s">
-        <v>936</v>
-      </c>
-      <c r="E251" t="s">
-        <v>937</v>
-      </c>
-      <c r="F251" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252">
-        <v>245</v>
-      </c>
-      <c r="B252">
-        <v>876</v>
-      </c>
-      <c r="C252" t="s">
-        <v>939</v>
-      </c>
-      <c r="D252"/>
-      <c r="E252" t="s">
-        <v>940</v>
-      </c>
-      <c r="F252" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253">
-        <v>246</v>
-      </c>
-      <c r="B253">
-        <v>882</v>
-      </c>
-      <c r="C253" t="s">
-        <v>942</v>
-      </c>
-      <c r="D253" t="s">
-        <v>943</v>
-      </c>
-      <c r="E253" t="s">
-        <v>944</v>
-      </c>
-      <c r="F253" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254">
-        <v>247</v>
-      </c>
-      <c r="B254">
-        <v>887</v>
-      </c>
-      <c r="C254" t="s">
-        <v>946</v>
-      </c>
-      <c r="D254" t="s">
-        <v>947</v>
-      </c>
-      <c r="E254" t="s">
-        <v>948</v>
-      </c>
-      <c r="F254" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255">
-        <v>248</v>
-      </c>
-      <c r="B255">
-        <v>894</v>
-      </c>
-      <c r="C255" t="s">
-        <v>950</v>
-      </c>
-      <c r="D255" t="s">
-        <v>951</v>
-      </c>
-      <c r="E255" t="s">
-        <v>952</v>
-      </c>
-      <c r="F255" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256">
-        <v>249</v>
-      </c>
-      <c r="B256">
-        <v>895</v>
-      </c>
-      <c r="C256" t="s">
-        <v>954</v>
-      </c>
-      <c r="D256" t="s">
-        <v>955</v>
-      </c>
-      <c r="E256" t="s">
-        <v>956</v>
-      </c>
-      <c r="F256" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257">
-        <v>250</v>
-      </c>
-      <c r="B257">
-        <v>896</v>
-      </c>
-      <c r="C257" t="s">
-        <v>958</v>
-      </c>
-      <c r="D257" t="s">
-        <v>959</v>
-      </c>
-      <c r="E257" t="s">
-        <v>960</v>
-      </c>
-      <c r="F257" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258">
-        <v>251</v>
-      </c>
-      <c r="B258">
-        <v>728</v>
-      </c>
-      <c r="C258" t="s">
-        <v>962</v>
-      </c>
-      <c r="D258" t="s">
-        <v>963</v>
-      </c>
-      <c r="E258" t="s">
-        <v>964</v>
-      </c>
-      <c r="F258" t="s">
-        <v>965</v>
+      <c r="C260" s="0" t="s">
+        <v>968</v>
+      </c>
+      <c r="D260" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="E260" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="F260" s="0" t="s">
+        <v>971</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <hyperlinks>
-    <hyperlink ref="A5" r:id="rId_hyperlink_1"/>
-  </hyperlinks>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName=""/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>973</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>976</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>977</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>980</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>981</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" s="0" t="s">
+        <v>982</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>984</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>985</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>986</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>987</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" s="0" t="s">
+        <v>988</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6" s="0" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>968</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7" s="0" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+    </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+    </row>
+  </sheetData>
+  <headerFooter/>
 </worksheet>
 </file>